--- a/data/BD_POs_Partidas_Detalladas.xlsx
+++ b/data/BD_POs_Partidas_Detalladas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
   <si>
     <t>id_partida</t>
   </si>
@@ -53,6 +53,72 @@
   </si>
   <si>
     <t>sku_cliente</t>
+  </si>
+  <si>
+    <t>26083177</t>
+  </si>
+  <si>
+    <t>12-D-6013-01</t>
+  </si>
+  <si>
+    <t>PP14873-01</t>
+  </si>
+  <si>
+    <t>PP14873-02</t>
+  </si>
+  <si>
+    <t>96-6183-01</t>
+  </si>
+  <si>
+    <t>P20325-24</t>
+  </si>
+  <si>
+    <t>P20325-25</t>
+  </si>
+  <si>
+    <t>EYES, LIFTING INDOOR SWBD (100/Bx)</t>
+  </si>
+  <si>
+    <t>46W STIFFENER</t>
+  </si>
+  <si>
+    <t>38W STIFFENER</t>
+  </si>
+  <si>
+    <t>MOUNTING BASE PAN</t>
+  </si>
+  <si>
+    <t>CT SUPPORT</t>
+  </si>
+  <si>
+    <t>CT BRACKET</t>
+  </si>
+  <si>
+    <t>PIEZA</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>SWB00454</t>
+  </si>
+  <si>
+    <t>SWB00686</t>
+  </si>
+  <si>
+    <t>SWB00924</t>
+  </si>
+  <si>
+    <t>SWB01469</t>
+  </si>
+  <si>
+    <t>SWB02436</t>
+  </si>
+  <si>
+    <t>SWB02437</t>
   </si>
 </sst>
 </file>
@@ -384,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -428,6 +494,234 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:13">
+      <c r="A2">
+        <v>440</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>128</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
+        <v>51.66</v>
+      </c>
+      <c r="I2">
+        <v>6612.48</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
+        <v>441</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>333.09</v>
+      </c>
+      <c r="I3">
+        <v>10658.88</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4">
+        <v>442</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4">
+        <v>296.65</v>
+      </c>
+      <c r="I4">
+        <v>11866</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5">
+        <v>443</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>769.6900000000001</v>
+      </c>
+      <c r="I5">
+        <v>30787.6</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6">
+        <v>444</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>64</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6">
+        <v>449.01</v>
+      </c>
+      <c r="I6">
+        <v>28736.64</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7">
+        <v>445</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7">
+        <v>53</v>
+      </c>
+      <c r="I7">
+        <v>3392</v>
+      </c>
+      <c r="J7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BD_POs_Partidas_Detalladas.xlsx
+++ b/data/BD_POs_Partidas_Detalladas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
   <si>
     <t>id_partida</t>
   </si>
@@ -58,6 +58,9 @@
     <t>26083177</t>
   </si>
   <si>
+    <t>26083235</t>
+  </si>
+  <si>
     <t>12-D-6013-01</t>
   </si>
   <si>
@@ -76,6 +79,15 @@
     <t>P20325-25</t>
   </si>
   <si>
+    <t>12-6355-03</t>
+  </si>
+  <si>
+    <t>12-6355-02</t>
+  </si>
+  <si>
+    <t>PP22114-05</t>
+  </si>
+  <si>
     <t>EYES, LIFTING INDOOR SWBD (100/Bx)</t>
   </si>
   <si>
@@ -94,10 +106,22 @@
     <t>CT BRACKET</t>
   </si>
   <si>
+    <t>15.0 INCH BLANK DOOR</t>
+  </si>
+  <si>
+    <t>DISTRIBUTION DOOR (NON WELDED)</t>
+  </si>
+  <si>
+    <t>382 X 15H INSTRUMENT DOOR</t>
+  </si>
+  <si>
     <t>PIEZA</t>
   </si>
   <si>
     <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
   </si>
   <si>
     <t>P1</t>
@@ -450,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -505,16 +529,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>128</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H2">
         <v>51.66</v>
@@ -523,13 +547,13 @@
         <v>6612.48</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -543,16 +567,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H3">
         <v>333.09</v>
@@ -561,13 +585,13 @@
         <v>10658.88</v>
       </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -581,16 +605,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H4">
         <v>296.65</v>
@@ -599,13 +623,13 @@
         <v>11866</v>
       </c>
       <c r="J4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -619,16 +643,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F5">
         <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H5">
         <v>769.6900000000001</v>
@@ -637,13 +661,13 @@
         <v>30787.6</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -657,16 +681,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F6">
         <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H6">
         <v>449.01</v>
@@ -675,13 +699,13 @@
         <v>28736.64</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -695,16 +719,16 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H7">
         <v>53</v>
@@ -713,13 +737,127 @@
         <v>3392</v>
       </c>
       <c r="J7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8">
+        <v>446</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8">
+        <v>295.5</v>
+      </c>
+      <c r="I8">
+        <v>9456</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9">
+        <v>447</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9">
+        <v>315</v>
+      </c>
+      <c r="I9">
+        <v>12600</v>
+      </c>
+      <c r="J9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10">
+        <v>448</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10">
+        <v>40</v>
+      </c>
+      <c r="G10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10">
+        <v>320.19</v>
+      </c>
+      <c r="I10">
+        <v>12807.85</v>
+      </c>
+      <c r="J10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_POs_Partidas_Detalladas.xlsx
+++ b/data/BD_POs_Partidas_Detalladas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
   <si>
     <t>id_partida</t>
   </si>
@@ -61,6 +61,9 @@
     <t>26083235</t>
   </si>
   <si>
+    <t>26083261</t>
+  </si>
+  <si>
     <t>12-D-6013-01</t>
   </si>
   <si>
@@ -88,6 +91,15 @@
     <t>PP22114-05</t>
   </si>
   <si>
+    <t>12-D-6091-08</t>
+  </si>
+  <si>
+    <t>PP7517-10</t>
+  </si>
+  <si>
+    <t>PP7517-01</t>
+  </si>
+  <si>
     <t>EYES, LIFTING INDOOR SWBD (100/Bx)</t>
   </si>
   <si>
@@ -115,6 +127,15 @@
     <t>382 X 15H INSTRUMENT DOOR</t>
   </si>
   <si>
+    <t>12-D-6091-08 PANEL DE CONTROL LC8</t>
+  </si>
+  <si>
+    <t>PP7517-10 SOPORTE SUPERIOR LC8</t>
+  </si>
+  <si>
+    <t>PP7517-01 BASE INFERIOR LC8</t>
+  </si>
+  <si>
     <t>PIEZA</t>
   </si>
   <si>
@@ -122,6 +143,9 @@
   </si>
   <si>
     <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
   </si>
   <si>
     <t>P1</t>
@@ -474,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -529,16 +553,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F2">
         <v>128</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H2">
         <v>51.66</v>
@@ -547,13 +571,13 @@
         <v>6612.48</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -567,16 +591,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>333.09</v>
@@ -585,13 +609,13 @@
         <v>10658.88</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -605,16 +629,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H4">
         <v>296.65</v>
@@ -623,13 +647,13 @@
         <v>11866</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -643,16 +667,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H5">
         <v>769.6900000000001</v>
@@ -661,13 +685,13 @@
         <v>30787.6</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -681,16 +705,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>449.01</v>
@@ -699,13 +723,13 @@
         <v>28736.64</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -719,16 +743,16 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H7">
         <v>53</v>
@@ -737,13 +761,13 @@
         <v>3392</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -757,16 +781,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H8">
         <v>295.5</v>
@@ -775,13 +799,13 @@
         <v>9456</v>
       </c>
       <c r="J8" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -795,16 +819,16 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H9">
         <v>315</v>
@@ -813,13 +837,13 @@
         <v>12600</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -833,16 +857,16 @@
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F10">
         <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H10">
         <v>320.19</v>
@@ -851,13 +875,127 @@
         <v>12807.85</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K10" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11">
+        <v>449</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11">
+        <v>420.5</v>
+      </c>
+      <c r="I11">
+        <v>8410</v>
+      </c>
+      <c r="J11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12">
+        <v>450</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12">
+        <v>285</v>
+      </c>
+      <c r="I12">
+        <v>9120</v>
+      </c>
+      <c r="J12" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13">
+        <v>451</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13">
+        <v>64</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13">
+        <v>195.75</v>
+      </c>
+      <c r="I13">
+        <v>12528</v>
+      </c>
+      <c r="J13" t="s">
+        <v>43</v>
+      </c>
+      <c r="K13" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_POs_Partidas_Detalladas.xlsx
+++ b/data/BD_POs_Partidas_Detalladas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="76">
   <si>
     <t>id_partida</t>
   </si>
@@ -55,6 +55,18 @@
     <t>sku_cliente</t>
   </si>
   <si>
+    <t>26083186</t>
+  </si>
+  <si>
+    <t>26083189</t>
+  </si>
+  <si>
+    <t>26083190</t>
+  </si>
+  <si>
+    <t>26083191</t>
+  </si>
+  <si>
     <t>26083177</t>
   </si>
   <si>
@@ -64,6 +76,21 @@
     <t>26083261</t>
   </si>
   <si>
+    <t>26083358</t>
+  </si>
+  <si>
+    <t>PP19380-03</t>
+  </si>
+  <si>
+    <t>11-7761-02</t>
+  </si>
+  <si>
+    <t>11-A-6014-01</t>
+  </si>
+  <si>
+    <t>11-A-9836-01</t>
+  </si>
+  <si>
     <t>12-D-6013-01</t>
   </si>
   <si>
@@ -73,15 +100,15 @@
     <t>PP14873-02</t>
   </si>
   <si>
+    <t>P20325-25</t>
+  </si>
+  <si>
+    <t>P20325-24</t>
+  </si>
+  <si>
     <t>96-6183-01</t>
   </si>
   <si>
-    <t>P20325-24</t>
-  </si>
-  <si>
-    <t>P20325-25</t>
-  </si>
-  <si>
     <t>12-6355-03</t>
   </si>
   <si>
@@ -100,28 +127,31 @@
     <t>PP7517-01</t>
   </si>
   <si>
-    <t>EYES, LIFTING INDOOR SWBD (100/Bx)</t>
-  </si>
-  <si>
-    <t>46W STIFFENER</t>
-  </si>
-  <si>
-    <t>38W STIFFENER</t>
-  </si>
-  <si>
-    <t>MOUNTING BASE PAN</t>
-  </si>
-  <si>
-    <t>CT SUPPORT</t>
-  </si>
-  <si>
-    <t>CT BRACKET</t>
+    <t>P9711-081 TRTO1</t>
+  </si>
+  <si>
+    <t>PP10218-13-TBC3</t>
+  </si>
+  <si>
+    <t>PP21139-081 TRTO</t>
+  </si>
+  <si>
+    <t>382 X 10H BLANK DOOR</t>
+  </si>
+  <si>
+    <t>11-7761-02 SOPORTE DE FIJACION META</t>
+  </si>
+  <si>
+    <t>11-7761-02 SOPORTE DE FIJACION CLOUD</t>
+  </si>
+  <si>
+    <t>11-A-6014-01 TAPA LATERAL LC8</t>
   </si>
   <si>
     <t>15.0 INCH BLANK DOOR</t>
   </si>
   <si>
-    <t>DISTRIBUTION DOOR (NON WELDED)</t>
+    <t>DISTRIBUTION DOOR NON WELDED</t>
   </si>
   <si>
     <t>382 X 15H INSTRUMENT DOOR</t>
@@ -136,10 +166,22 @@
     <t>PP7517-01 BASE INFERIOR LC8</t>
   </si>
   <si>
+    <t>REAR DOOR BOLTED LOUVERED 22 INCH</t>
+  </si>
+  <si>
+    <t>PLATE 70 &amp; 75 SP REAR TOP RH END</t>
+  </si>
+  <si>
+    <t>22W BREAKER DOOR W INSERT IP55 COVER</t>
+  </si>
+  <si>
     <t>PIEZA</t>
   </si>
   <si>
-    <t>2026-08-30</t>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
   </si>
   <si>
     <t>2026-08-28</t>
@@ -148,25 +190,58 @@
     <t>2026-08-31</t>
   </si>
   <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
     <t>P1</t>
   </si>
   <si>
-    <t>SWB00454</t>
-  </si>
-  <si>
-    <t>SWB00686</t>
-  </si>
-  <si>
-    <t>SWB00924</t>
-  </si>
-  <si>
-    <t>SWB01469</t>
-  </si>
-  <si>
-    <t>SWB02436</t>
-  </si>
-  <si>
-    <t>SWB02437</t>
+    <t>SWB01431</t>
+  </si>
+  <si>
+    <t>ISSIV05401</t>
+  </si>
+  <si>
+    <t>ISSIV05499</t>
+  </si>
+  <si>
+    <t>ISSIV00055</t>
+  </si>
+  <si>
+    <t>ISSIV00056</t>
+  </si>
+  <si>
+    <t>ISSIV00057</t>
+  </si>
+  <si>
+    <t>ISSIV00058</t>
+  </si>
+  <si>
+    <t>ISSIV00059</t>
+  </si>
+  <si>
+    <t>ISSIV00060</t>
+  </si>
+  <si>
+    <t>ISSIV00061</t>
+  </si>
+  <si>
+    <t>ISSIV00635</t>
+  </si>
+  <si>
+    <t>ISSIV00636</t>
+  </si>
+  <si>
+    <t>ISSIV00637</t>
+  </si>
+  <si>
+    <t>ISSIV06049</t>
+  </si>
+  <si>
+    <t>ISSIV05291</t>
+  </si>
+  <si>
+    <t>ISSIV06050</t>
   </si>
 </sst>
 </file>
@@ -498,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -544,7 +619,7 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -553,449 +628,753 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H2">
-        <v>51.66</v>
+        <v>345.5</v>
       </c>
       <c r="I2">
-        <v>6612.48</v>
+        <v>11056</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H3">
-        <v>333.09</v>
+        <v>290</v>
       </c>
       <c r="I3">
-        <v>10658.88</v>
+        <v>2320</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="K3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F4">
         <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H4">
-        <v>296.65</v>
+        <v>290</v>
       </c>
       <c r="I4">
-        <v>11866</v>
+        <v>11600</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="K4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H5">
-        <v>769.6900000000001</v>
+        <v>850</v>
       </c>
       <c r="I5">
-        <v>30787.6</v>
+        <v>850</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M5" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H6">
-        <v>449.01</v>
+        <v>1089.57</v>
       </c>
       <c r="I6">
-        <v>28736.64</v>
+        <v>17433.12</v>
       </c>
       <c r="J6" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M6" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F7">
+        <v>128</v>
+      </c>
+      <c r="G7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7">
+        <v>185.2</v>
+      </c>
+      <c r="I7">
+        <v>23705.6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" t="s">
         <v>64</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7">
-        <v>53</v>
-      </c>
-      <c r="I7">
-        <v>3392</v>
-      </c>
-      <c r="J7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" t="s">
-        <v>44</v>
-      </c>
-      <c r="M7" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H8">
-        <v>295.5</v>
+        <v>245.8</v>
       </c>
       <c r="I8">
-        <v>9456</v>
+        <v>7865.6</v>
       </c>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M8" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H9">
-        <v>315</v>
+        <v>255.4</v>
       </c>
       <c r="I9">
-        <v>12600</v>
+        <v>10216</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H10">
-        <v>320.19</v>
+        <v>295</v>
       </c>
       <c r="I10">
-        <v>12807.85</v>
+        <v>18880</v>
       </c>
       <c r="J10" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M10" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H11">
-        <v>420.5</v>
+        <v>295</v>
       </c>
       <c r="I11">
-        <v>8410</v>
+        <v>18880</v>
       </c>
       <c r="J11" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="H12">
-        <v>285</v>
+        <v>245</v>
       </c>
       <c r="I12">
-        <v>9120</v>
+        <v>9800</v>
       </c>
       <c r="J12" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K12" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13">
+        <v>320.5</v>
+      </c>
+      <c r="I13">
+        <v>10256</v>
+      </c>
+      <c r="J13" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14">
+        <v>464</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>40</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14">
+        <v>345</v>
+      </c>
+      <c r="I14">
+        <v>13800</v>
+      </c>
+      <c r="J14" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15">
+        <v>465</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
         <v>3</v>
       </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15">
+        <v>40</v>
+      </c>
+      <c r="G15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15">
+        <v>270.2</v>
+      </c>
+      <c r="I15">
+        <v>10807.85</v>
+      </c>
+      <c r="J15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16">
+        <v>466</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16">
+        <v>420.5</v>
+      </c>
+      <c r="I16">
+        <v>8410</v>
+      </c>
+      <c r="J16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17">
+        <v>467</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17">
+        <v>285</v>
+      </c>
+      <c r="I17">
+        <v>9120</v>
+      </c>
+      <c r="J17" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18">
+        <v>468</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18">
+        <v>64</v>
+      </c>
+      <c r="G18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18">
+        <v>195.75</v>
+      </c>
+      <c r="I18">
+        <v>12528</v>
+      </c>
+      <c r="J18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19">
+        <v>469</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>53</v>
+      </c>
+      <c r="H19">
+        <v>1250</v>
+      </c>
+      <c r="I19">
+        <v>1250</v>
+      </c>
+      <c r="J19" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20">
+        <v>470</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20">
+        <v>680</v>
+      </c>
+      <c r="I20">
+        <v>680</v>
+      </c>
+      <c r="J20" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21">
+        <v>471</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
         <v>39</v>
       </c>
-      <c r="F13">
-        <v>64</v>
-      </c>
-      <c r="G13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13">
-        <v>195.75</v>
-      </c>
-      <c r="I13">
-        <v>12528</v>
-      </c>
-      <c r="J13" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" t="s">
-        <v>44</v>
-      </c>
-      <c r="M13" t="s">
-        <v>27</v>
+      <c r="E21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21">
+        <v>890</v>
+      </c>
+      <c r="I21">
+        <v>10680</v>
+      </c>
+      <c r="J21" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_POs_Partidas_Detalladas.xlsx
+++ b/data/BD_POs_Partidas_Detalladas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="181">
   <si>
     <t>id_partida</t>
   </si>
@@ -79,6 +79,9 @@
     <t>26083358</t>
   </si>
   <si>
+    <t>26083425</t>
+  </si>
+  <si>
     <t>PP19380-03</t>
   </si>
   <si>
@@ -136,6 +139,108 @@
     <t>PP21139-081 TRTO</t>
   </si>
   <si>
+    <t>11-D-6165-01</t>
+  </si>
+  <si>
+    <t>11-A-6037-01</t>
+  </si>
+  <si>
+    <t>12-6267-01</t>
+  </si>
+  <si>
+    <t>12-6265-01</t>
+  </si>
+  <si>
+    <t>PP14112-19</t>
+  </si>
+  <si>
+    <t>P17311-17</t>
+  </si>
+  <si>
+    <t>11-A-6030-01</t>
+  </si>
+  <si>
+    <t>PP20204-06</t>
+  </si>
+  <si>
+    <t>PP20203-06</t>
+  </si>
+  <si>
+    <t>P20153S-04</t>
+  </si>
+  <si>
+    <t>P20321S-05</t>
+  </si>
+  <si>
+    <t>P20321S-06</t>
+  </si>
+  <si>
+    <t>12-6383-01</t>
+  </si>
+  <si>
+    <t>12-D-6234-08</t>
+  </si>
+  <si>
+    <t>12-D-6234-06</t>
+  </si>
+  <si>
+    <t>12-D-6234-10</t>
+  </si>
+  <si>
+    <t>13-D-6195-01</t>
+  </si>
+  <si>
+    <t>13-D-6196-01</t>
+  </si>
+  <si>
+    <t>PP20204-12</t>
+  </si>
+  <si>
+    <t>PP20204-13</t>
+  </si>
+  <si>
+    <t>PP20203-12</t>
+  </si>
+  <si>
+    <t>PP20203-13</t>
+  </si>
+  <si>
+    <t>PP13949-04</t>
+  </si>
+  <si>
+    <t>PP13949-08</t>
+  </si>
+  <si>
+    <t>PP13949-09</t>
+  </si>
+  <si>
+    <t>PP13949-10</t>
+  </si>
+  <si>
+    <t>96-6183-02</t>
+  </si>
+  <si>
+    <t>P20321-15-11</t>
+  </si>
+  <si>
+    <t>P20321-15-12</t>
+  </si>
+  <si>
+    <t>P20512-06</t>
+  </si>
+  <si>
+    <t>P20512-07</t>
+  </si>
+  <si>
+    <t>P20512-08</t>
+  </si>
+  <si>
+    <t>P20512-09</t>
+  </si>
+  <si>
+    <t>P20512-18</t>
+  </si>
+  <si>
     <t>382 X 10H BLANK DOOR</t>
   </si>
   <si>
@@ -175,6 +280,111 @@
     <t>22W BREAKER DOOR W INSERT IP55 COVER</t>
   </si>
   <si>
+    <t>BUSWAY COLLECTOR BRACKET</t>
+  </si>
+  <si>
+    <t>BARRIER CLIP CT THRU BUS</t>
+  </si>
+  <si>
+    <t>MTG. BRKT G.F. ENCLOSURE</t>
+  </si>
+  <si>
+    <t>TOP &amp; BOTTOM G.F. ENCLOSURE</t>
+  </si>
+  <si>
+    <t>SIDE SUPPORT</t>
+  </si>
+  <si>
+    <t>THRU BUS RISER SUPPORT ANGLE</t>
+  </si>
+  <si>
+    <t>11-A-6030-01 SOPORTE</t>
+  </si>
+  <si>
+    <t>PP20204-06 TAPA SUPERIOR</t>
+  </si>
+  <si>
+    <t>PP20203-06 TAPA INFERIOR</t>
+  </si>
+  <si>
+    <t>P20153S-04 PERFIL ESTRUCTURAL</t>
+  </si>
+  <si>
+    <t>P20321S-05 SOPORTE AISLADOR</t>
+  </si>
+  <si>
+    <t>P20321S-06 SOPORTE AISLADOR</t>
+  </si>
+  <si>
+    <t>12-6383-01 CANAL GUIA</t>
+  </si>
+  <si>
+    <t>12-D-6234-08 CANAL MONTAJE</t>
+  </si>
+  <si>
+    <t>12-D-6234-06 CANAL MONTAJE</t>
+  </si>
+  <si>
+    <t>12-D-6234-10 CANAL MONTAJE</t>
+  </si>
+  <si>
+    <t>13-D-6195-01 REFUERZO</t>
+  </si>
+  <si>
+    <t>13-D-6196-01 REFUERZO</t>
+  </si>
+  <si>
+    <t>PP20204-12 SOPORTE BUS</t>
+  </si>
+  <si>
+    <t>PP20204-13 SOPORTE BUS</t>
+  </si>
+  <si>
+    <t>PP20203-12 SOPORTE BUS</t>
+  </si>
+  <si>
+    <t>PP20203-13 SOPORTE BUS</t>
+  </si>
+  <si>
+    <t>PP13949-04 PLACA SEPARADORA</t>
+  </si>
+  <si>
+    <t>PP13949-08 PLACA SEPARADORA</t>
+  </si>
+  <si>
+    <t>PP13949-09 PLACA SEPARADORA</t>
+  </si>
+  <si>
+    <t>PP13949-10 PLACA SEPARADORA</t>
+  </si>
+  <si>
+    <t>96-6183-01 OREJA IZAJE</t>
+  </si>
+  <si>
+    <t>96-6183-02 OREJA IZAJE</t>
+  </si>
+  <si>
+    <t>P20321-15-11 SOPORTE BARRA</t>
+  </si>
+  <si>
+    <t>P20321-15-12 SOPORTE BARRA</t>
+  </si>
+  <si>
+    <t>P20512-06 SEPARADOR</t>
+  </si>
+  <si>
+    <t>P20512-07 SEPARADOR</t>
+  </si>
+  <si>
+    <t>P20512-08 SEPARADOR</t>
+  </si>
+  <si>
+    <t>P20512-09 SEPARADOR</t>
+  </si>
+  <si>
+    <t>P20512-18 SEPARADOR</t>
+  </si>
+  <si>
     <t>PIEZA</t>
   </si>
   <si>
@@ -242,6 +452,111 @@
   </si>
   <si>
     <t>ISSIV06050</t>
+  </si>
+  <si>
+    <t>SWB02031</t>
+  </si>
+  <si>
+    <t>SWB02030</t>
+  </si>
+  <si>
+    <t>SWB01162</t>
+  </si>
+  <si>
+    <t>SWB01161</t>
+  </si>
+  <si>
+    <t>SWB02052</t>
+  </si>
+  <si>
+    <t>SWB02035</t>
+  </si>
+  <si>
+    <t>SWB02036</t>
+  </si>
+  <si>
+    <t>SWB02037</t>
+  </si>
+  <si>
+    <t>SWB02038</t>
+  </si>
+  <si>
+    <t>SWB02039</t>
+  </si>
+  <si>
+    <t>SWB02040</t>
+  </si>
+  <si>
+    <t>SWB02041</t>
+  </si>
+  <si>
+    <t>SWB02042</t>
+  </si>
+  <si>
+    <t>SWB02043</t>
+  </si>
+  <si>
+    <t>SWB02044</t>
+  </si>
+  <si>
+    <t>SWB02045</t>
+  </si>
+  <si>
+    <t>SWB02046</t>
+  </si>
+  <si>
+    <t>SWB02047</t>
+  </si>
+  <si>
+    <t>SWB02048</t>
+  </si>
+  <si>
+    <t>SWB02049</t>
+  </si>
+  <si>
+    <t>SWB02050</t>
+  </si>
+  <si>
+    <t>SWB02051</t>
+  </si>
+  <si>
+    <t>SWB02053</t>
+  </si>
+  <si>
+    <t>SWB02054</t>
+  </si>
+  <si>
+    <t>SWB02055</t>
+  </si>
+  <si>
+    <t>SWB02056</t>
+  </si>
+  <si>
+    <t>SWB02057</t>
+  </si>
+  <si>
+    <t>SWB02058</t>
+  </si>
+  <si>
+    <t>SWB02059</t>
+  </si>
+  <si>
+    <t>SWB02060</t>
+  </si>
+  <si>
+    <t>SWB02061</t>
+  </si>
+  <si>
+    <t>SWB02062</t>
+  </si>
+  <si>
+    <t>SWB02063</t>
+  </si>
+  <si>
+    <t>SWB02064</t>
+  </si>
+  <si>
+    <t>SWB02065</t>
   </si>
 </sst>
 </file>
@@ -573,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -628,16 +943,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="F2">
         <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H2">
         <v>345.5</v>
@@ -646,13 +961,13 @@
         <v>11056</v>
       </c>
       <c r="J2" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="K2" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M2" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -666,16 +981,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F3">
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H3">
         <v>290</v>
@@ -684,13 +999,13 @@
         <v>2320</v>
       </c>
       <c r="J3" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="K3" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M3" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -704,16 +1019,16 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F4">
         <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H4">
         <v>290</v>
@@ -722,13 +1037,13 @@
         <v>11600</v>
       </c>
       <c r="J4" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="K4" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M4" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -742,16 +1057,16 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H5">
         <v>850</v>
@@ -760,13 +1075,13 @@
         <v>850</v>
       </c>
       <c r="J5" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="K5" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M5" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -780,16 +1095,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H6">
         <v>1089.57</v>
@@ -798,13 +1113,13 @@
         <v>17433.12</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="K6" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M6" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -818,16 +1133,16 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>128</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H7">
         <v>185.2</v>
@@ -836,13 +1151,13 @@
         <v>23705.6</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="K7" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M7" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -856,16 +1171,16 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
         <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H8">
         <v>245.8</v>
@@ -874,13 +1189,13 @@
         <v>7865.6</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s">
-        <v>65</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -894,16 +1209,16 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H9">
         <v>255.4</v>
@@ -912,13 +1227,13 @@
         <v>10216</v>
       </c>
       <c r="J9" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="K9" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M9" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -932,16 +1247,16 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H10">
         <v>295</v>
@@ -950,13 +1265,13 @@
         <v>18880</v>
       </c>
       <c r="J10" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="K10" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M10" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -970,16 +1285,16 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H11">
         <v>295</v>
@@ -988,13 +1303,13 @@
         <v>18880</v>
       </c>
       <c r="J11" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="K11" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M11" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1008,16 +1323,16 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F12">
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H12">
         <v>245</v>
@@ -1026,13 +1341,13 @@
         <v>9800</v>
       </c>
       <c r="J12" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="K12" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M12" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1046,16 +1361,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="F13">
         <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H13">
         <v>320.5</v>
@@ -1064,13 +1379,13 @@
         <v>10256</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="K13" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M13" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1084,16 +1399,16 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F14">
         <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H14">
         <v>345</v>
@@ -1102,13 +1417,13 @@
         <v>13800</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="K14" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M14" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1122,16 +1437,16 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="F15">
         <v>40</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H15">
         <v>270.2</v>
@@ -1140,13 +1455,13 @@
         <v>10807.85</v>
       </c>
       <c r="J15" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="K15" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M15" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1160,16 +1475,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="F16">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H16">
         <v>420.5</v>
@@ -1178,13 +1493,13 @@
         <v>8410</v>
       </c>
       <c r="J16" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="K16" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1198,16 +1513,16 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="F17">
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H17">
         <v>285</v>
@@ -1216,13 +1531,13 @@
         <v>9120</v>
       </c>
       <c r="J17" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="K17" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1236,16 +1551,16 @@
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F18">
         <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H18">
         <v>195.75</v>
@@ -1254,13 +1569,13 @@
         <v>12528</v>
       </c>
       <c r="J18" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="K18" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1274,16 +1589,16 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H19">
         <v>1250</v>
@@ -1292,13 +1607,13 @@
         <v>1250</v>
       </c>
       <c r="J19" t="s">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="K19" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M19" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1312,16 +1627,16 @@
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H20">
         <v>680</v>
@@ -1330,13 +1645,13 @@
         <v>680</v>
       </c>
       <c r="J20" t="s">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="K20" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="M20" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1350,16 +1665,16 @@
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="F21">
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="H21">
         <v>890</v>
@@ -1368,13 +1683,1343 @@
         <v>10680</v>
       </c>
       <c r="J21" t="s">
+        <v>128</v>
+      </c>
+      <c r="K21" t="s">
+        <v>129</v>
+      </c>
+      <c r="M21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22">
+        <v>472</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22">
+        <v>320</v>
+      </c>
+      <c r="G22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H22">
+        <v>185</v>
+      </c>
+      <c r="I22">
+        <v>59200</v>
+      </c>
+      <c r="J22" t="s">
+        <v>127</v>
+      </c>
+      <c r="K22" t="s">
+        <v>129</v>
+      </c>
+      <c r="M22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23">
+        <v>473</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23">
+        <v>192</v>
+      </c>
+      <c r="G23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23">
+        <v>145</v>
+      </c>
+      <c r="I23">
+        <v>27840</v>
+      </c>
+      <c r="J23" t="s">
+        <v>127</v>
+      </c>
+      <c r="K23" t="s">
+        <v>129</v>
+      </c>
+      <c r="M23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24">
+        <v>474</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24">
+        <v>224</v>
+      </c>
+      <c r="G24" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24">
+        <v>210</v>
+      </c>
+      <c r="I24">
+        <v>47040</v>
+      </c>
+      <c r="J24" t="s">
+        <v>127</v>
+      </c>
+      <c r="K24" t="s">
+        <v>129</v>
+      </c>
+      <c r="M24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25">
+        <v>475</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25">
+        <v>224</v>
+      </c>
+      <c r="G25" t="s">
+        <v>123</v>
+      </c>
+      <c r="H25">
+        <v>210</v>
+      </c>
+      <c r="I25">
+        <v>47040</v>
+      </c>
+      <c r="J25" t="s">
+        <v>127</v>
+      </c>
+      <c r="K25" t="s">
+        <v>129</v>
+      </c>
+      <c r="M25" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26">
+        <v>476</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26">
+        <v>160</v>
+      </c>
+      <c r="G26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26">
+        <v>175</v>
+      </c>
+      <c r="I26">
+        <v>28000</v>
+      </c>
+      <c r="J26" t="s">
+        <v>127</v>
+      </c>
+      <c r="K26" t="s">
+        <v>129</v>
+      </c>
+      <c r="M26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27">
+        <v>477</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27">
+        <v>160</v>
+      </c>
+      <c r="G27" t="s">
+        <v>123</v>
+      </c>
+      <c r="H27">
+        <v>165</v>
+      </c>
+      <c r="I27">
+        <v>26400</v>
+      </c>
+      <c r="J27" t="s">
+        <v>127</v>
+      </c>
+      <c r="K27" t="s">
+        <v>129</v>
+      </c>
+      <c r="M27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28">
+        <v>478</v>
+      </c>
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28">
+        <v>160</v>
+      </c>
+      <c r="G28" t="s">
+        <v>123</v>
+      </c>
+      <c r="H28">
+        <v>140</v>
+      </c>
+      <c r="I28">
+        <v>22400</v>
+      </c>
+      <c r="J28" t="s">
+        <v>127</v>
+      </c>
+      <c r="K28" t="s">
+        <v>129</v>
+      </c>
+      <c r="M28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29">
+        <v>479</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s">
+        <v>123</v>
+      </c>
+      <c r="H29">
+        <v>195</v>
+      </c>
+      <c r="I29">
+        <v>15600</v>
+      </c>
+      <c r="J29" t="s">
+        <v>127</v>
+      </c>
+      <c r="K29" t="s">
+        <v>129</v>
+      </c>
+      <c r="M29" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30">
+        <v>480</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s">
+        <v>123</v>
+      </c>
+      <c r="H30">
+        <v>195</v>
+      </c>
+      <c r="I30">
+        <v>15600</v>
+      </c>
+      <c r="J30" t="s">
+        <v>127</v>
+      </c>
+      <c r="K30" t="s">
+        <v>129</v>
+      </c>
+      <c r="M30" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31">
+        <v>481</v>
+      </c>
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31">
+        <v>120</v>
+      </c>
+      <c r="G31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H31">
+        <v>230</v>
+      </c>
+      <c r="I31">
+        <v>27600</v>
+      </c>
+      <c r="J31" t="s">
+        <v>127</v>
+      </c>
+      <c r="K31" t="s">
+        <v>129</v>
+      </c>
+      <c r="M31" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32">
+        <v>482</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32">
+        <v>120</v>
+      </c>
+      <c r="G32" t="s">
+        <v>123</v>
+      </c>
+      <c r="H32">
+        <v>215</v>
+      </c>
+      <c r="I32">
+        <v>25800</v>
+      </c>
+      <c r="J32" t="s">
+        <v>127</v>
+      </c>
+      <c r="K32" t="s">
+        <v>129</v>
+      </c>
+      <c r="M32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33">
+        <v>483</v>
+      </c>
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33">
+        <v>80</v>
+      </c>
+      <c r="G33" t="s">
+        <v>123</v>
+      </c>
+      <c r="H33">
+        <v>215</v>
+      </c>
+      <c r="I33">
+        <v>17200</v>
+      </c>
+      <c r="J33" t="s">
+        <v>127</v>
+      </c>
+      <c r="K33" t="s">
+        <v>129</v>
+      </c>
+      <c r="M33" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34">
+        <v>484</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s">
+        <v>123</v>
+      </c>
+      <c r="H34">
+        <v>155</v>
+      </c>
+      <c r="I34">
+        <v>12400</v>
+      </c>
+      <c r="J34" t="s">
+        <v>127</v>
+      </c>
+      <c r="K34" t="s">
+        <v>129</v>
+      </c>
+      <c r="M34" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35">
+        <v>485</v>
+      </c>
+      <c r="B35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" t="s">
+        <v>101</v>
+      </c>
+      <c r="F35">
+        <v>160</v>
+      </c>
+      <c r="G35" t="s">
+        <v>123</v>
+      </c>
+      <c r="H35">
+        <v>220</v>
+      </c>
+      <c r="I35">
+        <v>35200</v>
+      </c>
+      <c r="J35" t="s">
+        <v>127</v>
+      </c>
+      <c r="K35" t="s">
+        <v>129</v>
+      </c>
+      <c r="M35" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36">
+        <v>486</v>
+      </c>
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36">
+        <v>120</v>
+      </c>
+      <c r="G36" t="s">
+        <v>123</v>
+      </c>
+      <c r="H36">
+        <v>210</v>
+      </c>
+      <c r="I36">
+        <v>25200</v>
+      </c>
+      <c r="J36" t="s">
+        <v>127</v>
+      </c>
+      <c r="K36" t="s">
+        <v>129</v>
+      </c>
+      <c r="M36" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37">
+        <v>487</v>
+      </c>
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37">
+        <v>16</v>
+      </c>
+      <c r="D37" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37">
+        <v>240</v>
+      </c>
+      <c r="G37" t="s">
+        <v>123</v>
+      </c>
+      <c r="H37">
+        <v>245</v>
+      </c>
+      <c r="I37">
+        <v>58800</v>
+      </c>
+      <c r="J37" t="s">
+        <v>127</v>
+      </c>
+      <c r="K37" t="s">
+        <v>129</v>
+      </c>
+      <c r="M37" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38">
+        <v>488</v>
+      </c>
+      <c r="B38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38">
+        <v>17</v>
+      </c>
+      <c r="D38" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38">
+        <v>120</v>
+      </c>
+      <c r="G38" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38">
+        <v>180</v>
+      </c>
+      <c r="I38">
+        <v>21600</v>
+      </c>
+      <c r="J38" t="s">
+        <v>127</v>
+      </c>
+      <c r="K38" t="s">
+        <v>129</v>
+      </c>
+      <c r="M38" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39">
+        <v>489</v>
+      </c>
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
         <v>58</v>
       </c>
-      <c r="K21" t="s">
+      <c r="E39" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39">
+        <v>120</v>
+      </c>
+      <c r="G39" t="s">
+        <v>123</v>
+      </c>
+      <c r="H39">
+        <v>180</v>
+      </c>
+      <c r="I39">
+        <v>21600</v>
+      </c>
+      <c r="J39" t="s">
+        <v>127</v>
+      </c>
+      <c r="K39" t="s">
+        <v>129</v>
+      </c>
+      <c r="M39" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40">
+        <v>490</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
         <v>59</v>
       </c>
-      <c r="M21" t="s">
-        <v>75</v>
+      <c r="E40" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40">
+        <v>160</v>
+      </c>
+      <c r="G40" t="s">
+        <v>123</v>
+      </c>
+      <c r="H40">
+        <v>205</v>
+      </c>
+      <c r="I40">
+        <v>32800</v>
+      </c>
+      <c r="J40" t="s">
+        <v>127</v>
+      </c>
+      <c r="K40" t="s">
+        <v>129</v>
+      </c>
+      <c r="M40" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41">
+        <v>491</v>
+      </c>
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41">
+        <v>20</v>
+      </c>
+      <c r="D41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41">
+        <v>120</v>
+      </c>
+      <c r="G41" t="s">
+        <v>123</v>
+      </c>
+      <c r="H41">
+        <v>205</v>
+      </c>
+      <c r="I41">
+        <v>24600</v>
+      </c>
+      <c r="J41" t="s">
+        <v>127</v>
+      </c>
+      <c r="K41" t="s">
+        <v>129</v>
+      </c>
+      <c r="M41" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42">
+        <v>492</v>
+      </c>
+      <c r="B42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42">
+        <v>21</v>
+      </c>
+      <c r="D42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42">
+        <v>160</v>
+      </c>
+      <c r="G42" t="s">
+        <v>123</v>
+      </c>
+      <c r="H42">
+        <v>205</v>
+      </c>
+      <c r="I42">
+        <v>32800</v>
+      </c>
+      <c r="J42" t="s">
+        <v>127</v>
+      </c>
+      <c r="K42" t="s">
+        <v>129</v>
+      </c>
+      <c r="M42" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43">
+        <v>493</v>
+      </c>
+      <c r="B43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" t="s">
+        <v>109</v>
+      </c>
+      <c r="F43">
+        <v>120</v>
+      </c>
+      <c r="G43" t="s">
+        <v>123</v>
+      </c>
+      <c r="H43">
+        <v>205</v>
+      </c>
+      <c r="I43">
+        <v>24600</v>
+      </c>
+      <c r="J43" t="s">
+        <v>127</v>
+      </c>
+      <c r="K43" t="s">
+        <v>129</v>
+      </c>
+      <c r="M43" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44">
+        <v>494</v>
+      </c>
+      <c r="B44" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44">
+        <v>23</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s">
+        <v>123</v>
+      </c>
+      <c r="H44">
+        <v>135</v>
+      </c>
+      <c r="I44">
+        <v>10800</v>
+      </c>
+      <c r="J44" t="s">
+        <v>127</v>
+      </c>
+      <c r="K44" t="s">
+        <v>129</v>
+      </c>
+      <c r="M44" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45">
+        <v>495</v>
+      </c>
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45">
+        <v>24</v>
+      </c>
+      <c r="D45" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" t="s">
+        <v>111</v>
+      </c>
+      <c r="F45">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s">
+        <v>123</v>
+      </c>
+      <c r="H45">
+        <v>135</v>
+      </c>
+      <c r="I45">
+        <v>10800</v>
+      </c>
+      <c r="J45" t="s">
+        <v>127</v>
+      </c>
+      <c r="K45" t="s">
+        <v>129</v>
+      </c>
+      <c r="M45" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46">
+        <v>496</v>
+      </c>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46">
+        <v>25</v>
+      </c>
+      <c r="D46" t="s">
+        <v>65</v>
+      </c>
+      <c r="E46" t="s">
+        <v>112</v>
+      </c>
+      <c r="F46">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s">
+        <v>123</v>
+      </c>
+      <c r="H46">
+        <v>135</v>
+      </c>
+      <c r="I46">
+        <v>10800</v>
+      </c>
+      <c r="J46" t="s">
+        <v>127</v>
+      </c>
+      <c r="K46" t="s">
+        <v>129</v>
+      </c>
+      <c r="M46" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47">
+        <v>497</v>
+      </c>
+      <c r="B47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47">
+        <v>26</v>
+      </c>
+      <c r="D47" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47">
+        <v>160</v>
+      </c>
+      <c r="G47" t="s">
+        <v>123</v>
+      </c>
+      <c r="H47">
+        <v>140</v>
+      </c>
+      <c r="I47">
+        <v>22400</v>
+      </c>
+      <c r="J47" t="s">
+        <v>127</v>
+      </c>
+      <c r="K47" t="s">
+        <v>129</v>
+      </c>
+      <c r="M47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48">
+        <v>498</v>
+      </c>
+      <c r="B48" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48">
+        <v>27</v>
+      </c>
+      <c r="D48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" t="s">
+        <v>114</v>
+      </c>
+      <c r="F48">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s">
+        <v>123</v>
+      </c>
+      <c r="H48">
+        <v>160</v>
+      </c>
+      <c r="I48">
+        <v>12800</v>
+      </c>
+      <c r="J48" t="s">
+        <v>127</v>
+      </c>
+      <c r="K48" t="s">
+        <v>129</v>
+      </c>
+      <c r="M48" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49">
+        <v>499</v>
+      </c>
+      <c r="B49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49">
+        <v>28</v>
+      </c>
+      <c r="D49" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" t="s">
+        <v>115</v>
+      </c>
+      <c r="F49">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s">
+        <v>123</v>
+      </c>
+      <c r="H49">
+        <v>160</v>
+      </c>
+      <c r="I49">
+        <v>12800</v>
+      </c>
+      <c r="J49" t="s">
+        <v>127</v>
+      </c>
+      <c r="K49" t="s">
+        <v>129</v>
+      </c>
+      <c r="M49" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50">
+        <v>500</v>
+      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50">
+        <v>29</v>
+      </c>
+      <c r="D50" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s">
+        <v>123</v>
+      </c>
+      <c r="H50">
+        <v>190</v>
+      </c>
+      <c r="I50">
+        <v>15200</v>
+      </c>
+      <c r="J50" t="s">
+        <v>127</v>
+      </c>
+      <c r="K50" t="s">
+        <v>129</v>
+      </c>
+      <c r="M50" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51">
+        <v>501</v>
+      </c>
+      <c r="B51" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51">
+        <v>30</v>
+      </c>
+      <c r="D51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E51" t="s">
+        <v>117</v>
+      </c>
+      <c r="F51">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s">
+        <v>123</v>
+      </c>
+      <c r="H51">
+        <v>190</v>
+      </c>
+      <c r="I51">
+        <v>15200</v>
+      </c>
+      <c r="J51" t="s">
+        <v>127</v>
+      </c>
+      <c r="K51" t="s">
+        <v>129</v>
+      </c>
+      <c r="M51" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52">
+        <v>502</v>
+      </c>
+      <c r="B52" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52">
+        <v>31</v>
+      </c>
+      <c r="D52" t="s">
+        <v>70</v>
+      </c>
+      <c r="E52" t="s">
+        <v>118</v>
+      </c>
+      <c r="F52">
+        <v>160</v>
+      </c>
+      <c r="G52" t="s">
+        <v>123</v>
+      </c>
+      <c r="H52">
+        <v>115</v>
+      </c>
+      <c r="I52">
+        <v>18400</v>
+      </c>
+      <c r="J52" t="s">
+        <v>127</v>
+      </c>
+      <c r="K52" t="s">
+        <v>129</v>
+      </c>
+      <c r="M52" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53">
+        <v>503</v>
+      </c>
+      <c r="B53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53">
+        <v>32</v>
+      </c>
+      <c r="D53" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" t="s">
+        <v>119</v>
+      </c>
+      <c r="F53">
+        <v>160</v>
+      </c>
+      <c r="G53" t="s">
+        <v>123</v>
+      </c>
+      <c r="H53">
+        <v>115</v>
+      </c>
+      <c r="I53">
+        <v>18400</v>
+      </c>
+      <c r="J53" t="s">
+        <v>127</v>
+      </c>
+      <c r="K53" t="s">
+        <v>129</v>
+      </c>
+      <c r="M53" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54">
+        <v>504</v>
+      </c>
+      <c r="B54" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54">
+        <v>33</v>
+      </c>
+      <c r="D54" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" t="s">
+        <v>120</v>
+      </c>
+      <c r="F54">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s">
+        <v>123</v>
+      </c>
+      <c r="H54">
+        <v>115</v>
+      </c>
+      <c r="I54">
+        <v>9200</v>
+      </c>
+      <c r="J54" t="s">
+        <v>127</v>
+      </c>
+      <c r="K54" t="s">
+        <v>129</v>
+      </c>
+      <c r="M54" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55">
+        <v>505</v>
+      </c>
+      <c r="B55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55">
+        <v>34</v>
+      </c>
+      <c r="D55" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" t="s">
+        <v>121</v>
+      </c>
+      <c r="F55">
+        <v>160</v>
+      </c>
+      <c r="G55" t="s">
+        <v>123</v>
+      </c>
+      <c r="H55">
+        <v>115</v>
+      </c>
+      <c r="I55">
+        <v>18400</v>
+      </c>
+      <c r="J55" t="s">
+        <v>127</v>
+      </c>
+      <c r="K55" t="s">
+        <v>129</v>
+      </c>
+      <c r="M55" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56">
+        <v>506</v>
+      </c>
+      <c r="B56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56">
+        <v>35</v>
+      </c>
+      <c r="D56" t="s">
+        <v>74</v>
+      </c>
+      <c r="E56" t="s">
+        <v>122</v>
+      </c>
+      <c r="F56">
+        <v>120</v>
+      </c>
+      <c r="G56" t="s">
+        <v>123</v>
+      </c>
+      <c r="H56">
+        <v>125</v>
+      </c>
+      <c r="I56">
+        <v>15000</v>
+      </c>
+      <c r="J56" t="s">
+        <v>127</v>
+      </c>
+      <c r="K56" t="s">
+        <v>129</v>
+      </c>
+      <c r="M56" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_POs_Partidas_Detalladas.xlsx
+++ b/data/BD_POs_Partidas_Detalladas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="200">
   <si>
     <t>id_partida</t>
   </si>
@@ -160,16 +160,88 @@
     <t>11-A-6030-01</t>
   </si>
   <si>
+    <t>12-D-6015-05</t>
+  </si>
+  <si>
+    <t>12-D-6017-02</t>
+  </si>
+  <si>
+    <t>12-D-6234-08</t>
+  </si>
+  <si>
+    <t>P20512-09</t>
+  </si>
+  <si>
+    <t>P20512-06</t>
+  </si>
+  <si>
+    <t>P20512-07</t>
+  </si>
+  <si>
+    <t>PP20205-121</t>
+  </si>
+  <si>
+    <t>PP20204-12</t>
+  </si>
+  <si>
+    <t>PP20203-12</t>
+  </si>
+  <si>
+    <t>P20321-12</t>
+  </si>
+  <si>
+    <t>P20346-04</t>
+  </si>
+  <si>
+    <t>13-D-6196-01</t>
+  </si>
+  <si>
+    <t>P20512-18</t>
+  </si>
+  <si>
+    <t>13-D-6195-01</t>
+  </si>
+  <si>
+    <t>P20153S-04</t>
+  </si>
+  <si>
+    <t>P20321S-05</t>
+  </si>
+  <si>
+    <t>12-D-6234-06</t>
+  </si>
+  <si>
+    <t>PP20204-13</t>
+  </si>
+  <si>
+    <t>PP20203-13</t>
+  </si>
+  <si>
+    <t>PP13949-10</t>
+  </si>
+  <si>
+    <t>P20321-13</t>
+  </si>
+  <si>
+    <t>P20321-15-11</t>
+  </si>
+  <si>
+    <t>P20321-15-12</t>
+  </si>
+  <si>
+    <t>P20512-08</t>
+  </si>
+  <si>
+    <t>P20321-21</t>
+  </si>
+  <si>
     <t>PP20204-06</t>
   </si>
   <si>
     <t>PP20203-06</t>
   </si>
   <si>
-    <t>P20153S-04</t>
-  </si>
-  <si>
-    <t>P20321S-05</t>
+    <t>PP20205-061</t>
   </si>
   <si>
     <t>P20321S-06</t>
@@ -178,67 +250,25 @@
     <t>12-6383-01</t>
   </si>
   <si>
-    <t>12-D-6234-08</t>
-  </si>
-  <si>
-    <t>12-D-6234-06</t>
-  </si>
-  <si>
-    <t>12-D-6234-10</t>
-  </si>
-  <si>
-    <t>13-D-6195-01</t>
-  </si>
-  <si>
-    <t>13-D-6196-01</t>
-  </si>
-  <si>
-    <t>PP20204-12</t>
-  </si>
-  <si>
-    <t>PP20204-13</t>
-  </si>
-  <si>
-    <t>PP20203-12</t>
-  </si>
-  <si>
-    <t>PP20203-13</t>
-  </si>
-  <si>
     <t>PP13949-04</t>
   </si>
   <si>
+    <t>PP13949-09</t>
+  </si>
+  <si>
+    <t>PP20205-131</t>
+  </si>
+  <si>
+    <t>PP20205-132</t>
+  </si>
+  <si>
     <t>PP13949-08</t>
   </si>
   <si>
-    <t>PP13949-09</t>
-  </si>
-  <si>
-    <t>PP13949-10</t>
-  </si>
-  <si>
     <t>96-6183-02</t>
   </si>
   <si>
-    <t>P20321-15-11</t>
-  </si>
-  <si>
-    <t>P20321-15-12</t>
-  </si>
-  <si>
-    <t>P20512-06</t>
-  </si>
-  <si>
-    <t>P20512-07</t>
-  </si>
-  <si>
-    <t>P20512-08</t>
-  </si>
-  <si>
-    <t>P20512-09</t>
-  </si>
-  <si>
-    <t>P20512-18</t>
+    <t>P19663-24</t>
   </si>
   <si>
     <t>382 X 10H BLANK DOOR</t>
@@ -298,91 +328,88 @@
     <t>THRU BUS RISER SUPPORT ANGLE</t>
   </si>
   <si>
-    <t>11-A-6030-01 SOPORTE</t>
-  </si>
-  <si>
-    <t>PP20204-06 TAPA SUPERIOR</t>
-  </si>
-  <si>
-    <t>PP20203-06 TAPA INFERIOR</t>
-  </si>
-  <si>
-    <t>P20153S-04 PERFIL ESTRUCTURAL</t>
-  </si>
-  <si>
-    <t>P20321S-05 SOPORTE AISLADOR</t>
-  </si>
-  <si>
-    <t>P20321S-06 SOPORTE AISLADOR</t>
-  </si>
-  <si>
-    <t>12-6383-01 CANAL GUIA</t>
-  </si>
-  <si>
-    <t>12-D-6234-08 CANAL MONTAJE</t>
-  </si>
-  <si>
-    <t>12-D-6234-06 CANAL MONTAJE</t>
-  </si>
-  <si>
-    <t>12-D-6234-10 CANAL MONTAJE</t>
-  </si>
-  <si>
-    <t>13-D-6195-01 REFUERZO</t>
-  </si>
-  <si>
-    <t>13-D-6196-01 REFUERZO</t>
-  </si>
-  <si>
-    <t>PP20204-12 SOPORTE BUS</t>
-  </si>
-  <si>
-    <t>PP20204-13 SOPORTE BUS</t>
-  </si>
-  <si>
-    <t>PP20203-12 SOPORTE BUS</t>
-  </si>
-  <si>
-    <t>PP20203-13 SOPORTE BUS</t>
-  </si>
-  <si>
-    <t>PP13949-04 PLACA SEPARADORA</t>
-  </si>
-  <si>
-    <t>PP13949-08 PLACA SEPARADORA</t>
-  </si>
-  <si>
-    <t>PP13949-09 PLACA SEPARADORA</t>
-  </si>
-  <si>
-    <t>PP13949-10 PLACA SEPARADORA</t>
-  </si>
-  <si>
-    <t>96-6183-01 OREJA IZAJE</t>
-  </si>
-  <si>
-    <t>96-6183-02 OREJA IZAJE</t>
-  </si>
-  <si>
-    <t>P20321-15-11 SOPORTE BARRA</t>
-  </si>
-  <si>
-    <t>P20321-15-12 SOPORTE BARRA</t>
-  </si>
-  <si>
-    <t>P20512-06 SEPARADOR</t>
-  </si>
-  <si>
-    <t>P20512-07 SEPARADOR</t>
-  </si>
-  <si>
-    <t>P20512-08 SEPARADOR</t>
-  </si>
-  <si>
-    <t>P20512-09 SEPARADOR</t>
-  </si>
-  <si>
-    <t>P20512-18 SEPARADOR</t>
+    <t>800-2000A BPS BOND MTG BRKT</t>
+  </si>
+  <si>
+    <t>46 FRONT RING CHAN. HD</t>
+  </si>
+  <si>
+    <t>INTERIOR SUPT CROSS CHAN 38W</t>
+  </si>
+  <si>
+    <t>FRNT/REAR FLR PLATE ANGLE 12GA</t>
+  </si>
+  <si>
+    <t>MOUNTING BRACKET</t>
+  </si>
+  <si>
+    <t>SUPPORT</t>
+  </si>
+  <si>
+    <t>38W 22.5H 17D S2 FOLDING PAN</t>
+  </si>
+  <si>
+    <t>AUX COMP TOP PLATE</t>
+  </si>
+  <si>
+    <t>T/B SUPPORT CROSS CHANNEL</t>
+  </si>
+  <si>
+    <t>RISER SUPPORT</t>
+  </si>
+  <si>
+    <t>RUN BACK SUPPORT</t>
+  </si>
+  <si>
+    <t>BARRIER CLIP</t>
+  </si>
+  <si>
+    <t>FRONT/REAR FLOOR PLATE ANGLE</t>
+  </si>
+  <si>
+    <t>SIDE COVER</t>
+  </si>
+  <si>
+    <t>CT SUPPORT</t>
+  </si>
+  <si>
+    <t>COLLECTOR BUS SUPPORT</t>
+  </si>
+  <si>
+    <t>VERTICAL BUS SUPPORT - BUSWAY</t>
+  </si>
+  <si>
+    <t>AUX COMP BOTTOM PLATE 38W</t>
+  </si>
+  <si>
+    <t>AUX COMP TOP PLATE 38W</t>
+  </si>
+  <si>
+    <t>FOLDING AUX PAN, 38W</t>
+  </si>
+  <si>
+    <t>REAR BARRIER SUPPORT</t>
+  </si>
+  <si>
+    <t>MTG BASE PAN 7.5 IN BOX</t>
+  </si>
+  <si>
+    <t>BACK PAN</t>
+  </si>
+  <si>
+    <t>BOTTOM COVER</t>
+  </si>
+  <si>
+    <t>TOP COVER</t>
+  </si>
+  <si>
+    <t>MOUNTING BASE PAN</t>
+  </si>
+  <si>
+    <t>MOUNTING BASE PAN (G.F.)</t>
+  </si>
+  <si>
+    <t>AUX PAN</t>
   </si>
   <si>
     <t>PIEZA</t>
@@ -472,10 +499,67 @@
     <t>SWB02035</t>
   </si>
   <si>
+    <t>SWB02029</t>
+  </si>
+  <si>
+    <t>SWB00456</t>
+  </si>
+  <si>
+    <t>SWB01167</t>
+  </si>
+  <si>
+    <t>SWB01169</t>
+  </si>
+  <si>
+    <t>SWB02049</t>
+  </si>
+  <si>
+    <t>SWB02046</t>
+  </si>
+  <si>
+    <t>SWB02047</t>
+  </si>
+  <si>
+    <t>SWB01526</t>
+  </si>
+  <si>
+    <t>SWB01524</t>
+  </si>
+  <si>
+    <t>SWB01522</t>
+  </si>
+  <si>
+    <t>SWB02037</t>
+  </si>
+  <si>
+    <t>SWB02045</t>
+  </si>
+  <si>
+    <t>SWB02034</t>
+  </si>
+  <si>
+    <t>SWB02050</t>
+  </si>
+  <si>
+    <t>SWB02033</t>
+  </si>
+  <si>
     <t>SWB02036</t>
   </si>
   <si>
-    <t>SWB02037</t>
+    <t>SWB02042</t>
+  </si>
+  <si>
+    <t>SWB00488</t>
+  </si>
+  <si>
+    <t>SWB01525</t>
+  </si>
+  <si>
+    <t>SWB01523</t>
+  </si>
+  <si>
+    <t>SWB01518</t>
   </si>
   <si>
     <t>SWB02038</t>
@@ -487,76 +571,49 @@
     <t>SWB02040</t>
   </si>
   <si>
+    <t>SWB02048</t>
+  </si>
+  <si>
     <t>SWB02041</t>
   </si>
   <si>
-    <t>SWB02042</t>
+    <t>SWB02054</t>
+  </si>
+  <si>
+    <t>SWB02053</t>
+  </si>
+  <si>
+    <t>SWB02055</t>
   </si>
   <si>
     <t>SWB02043</t>
   </si>
   <si>
-    <t>SWB02044</t>
-  </si>
-  <si>
-    <t>SWB02045</t>
-  </si>
-  <si>
-    <t>SWB02046</t>
-  </si>
-  <si>
-    <t>SWB02047</t>
-  </si>
-  <si>
-    <t>SWB02048</t>
-  </si>
-  <si>
-    <t>SWB02049</t>
-  </si>
-  <si>
-    <t>SWB02050</t>
+    <t>SWB01944</t>
+  </si>
+  <si>
+    <t>SWB01515</t>
+  </si>
+  <si>
+    <t>SWB01517</t>
+  </si>
+  <si>
+    <t>SWB01528</t>
+  </si>
+  <si>
+    <t>SWB01529</t>
   </si>
   <si>
     <t>SWB02051</t>
   </si>
   <si>
-    <t>SWB02053</t>
-  </si>
-  <si>
-    <t>SWB02054</t>
-  </si>
-  <si>
-    <t>SWB02055</t>
-  </si>
-  <si>
-    <t>SWB02056</t>
-  </si>
-  <si>
-    <t>SWB02057</t>
-  </si>
-  <si>
-    <t>SWB02058</t>
-  </si>
-  <si>
-    <t>SWB02059</t>
-  </si>
-  <si>
-    <t>SWB02060</t>
-  </si>
-  <si>
-    <t>SWB02061</t>
-  </si>
-  <si>
-    <t>SWB02062</t>
-  </si>
-  <si>
-    <t>SWB02063</t>
-  </si>
-  <si>
-    <t>SWB02064</t>
-  </si>
-  <si>
-    <t>SWB02065</t>
+    <t>SWB01469</t>
+  </si>
+  <si>
+    <t>SWB01311</t>
+  </si>
+  <si>
+    <t>SWB01487</t>
   </si>
 </sst>
 </file>
@@ -888,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -946,13 +1003,13 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F2">
         <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H2">
         <v>345.5</v>
@@ -961,13 +1018,13 @@
         <v>11056</v>
       </c>
       <c r="J2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -984,13 +1041,13 @@
         <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F3">
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H3">
         <v>290</v>
@@ -999,13 +1056,13 @@
         <v>2320</v>
       </c>
       <c r="J3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1022,13 +1079,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F4">
         <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H4">
         <v>290</v>
@@ -1037,13 +1094,13 @@
         <v>11600</v>
       </c>
       <c r="J4" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1060,13 +1117,13 @@
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H5">
         <v>850</v>
@@ -1075,13 +1132,13 @@
         <v>850</v>
       </c>
       <c r="J5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1104,7 +1161,7 @@
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H6">
         <v>1089.57</v>
@@ -1113,13 +1170,13 @@
         <v>17433.12</v>
       </c>
       <c r="J6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K6" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M6" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1142,7 +1199,7 @@
         <v>128</v>
       </c>
       <c r="G7" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H7">
         <v>185.2</v>
@@ -1151,13 +1208,13 @@
         <v>23705.6</v>
       </c>
       <c r="J7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K7" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M7" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1180,7 +1237,7 @@
         <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H8">
         <v>245.8</v>
@@ -1189,13 +1246,13 @@
         <v>7865.6</v>
       </c>
       <c r="J8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K8" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M8" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1218,7 +1275,7 @@
         <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H9">
         <v>255.4</v>
@@ -1227,13 +1284,13 @@
         <v>10216</v>
       </c>
       <c r="J9" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K9" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1256,7 +1313,7 @@
         <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H10">
         <v>295</v>
@@ -1265,13 +1322,13 @@
         <v>18880</v>
       </c>
       <c r="J10" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K10" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M10" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1294,7 +1351,7 @@
         <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H11">
         <v>295</v>
@@ -1303,13 +1360,13 @@
         <v>18880</v>
       </c>
       <c r="J11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K11" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1332,7 +1389,7 @@
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H12">
         <v>245</v>
@@ -1341,13 +1398,13 @@
         <v>9800</v>
       </c>
       <c r="J12" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K12" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M12" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1364,13 +1421,13 @@
         <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F13">
         <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H13">
         <v>320.5</v>
@@ -1379,13 +1436,13 @@
         <v>10256</v>
       </c>
       <c r="J13" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K13" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M13" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1402,13 +1459,13 @@
         <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F14">
         <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H14">
         <v>345</v>
@@ -1417,13 +1474,13 @@
         <v>13800</v>
       </c>
       <c r="J14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K14" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1440,13 +1497,13 @@
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F15">
         <v>40</v>
       </c>
       <c r="G15" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H15">
         <v>270.2</v>
@@ -1455,13 +1512,13 @@
         <v>10807.85</v>
       </c>
       <c r="J15" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K15" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1478,13 +1535,13 @@
         <v>35</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F16">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H16">
         <v>420.5</v>
@@ -1493,10 +1550,10 @@
         <v>8410</v>
       </c>
       <c r="J16" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K16" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M16" t="s">
         <v>35</v>
@@ -1516,13 +1573,13 @@
         <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F17">
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H17">
         <v>285</v>
@@ -1531,10 +1588,10 @@
         <v>9120</v>
       </c>
       <c r="J17" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K17" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M17" t="s">
         <v>36</v>
@@ -1554,13 +1611,13 @@
         <v>37</v>
       </c>
       <c r="E18" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F18">
         <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H18">
         <v>195.75</v>
@@ -1569,10 +1626,10 @@
         <v>12528</v>
       </c>
       <c r="J18" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K18" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s">
         <v>37</v>
@@ -1592,13 +1649,13 @@
         <v>38</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H19">
         <v>1250</v>
@@ -1607,13 +1664,13 @@
         <v>1250</v>
       </c>
       <c r="J19" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="K19" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1630,13 +1687,13 @@
         <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H20">
         <v>680</v>
@@ -1645,13 +1702,13 @@
         <v>680</v>
       </c>
       <c r="J20" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="K20" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M20" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1668,13 +1725,13 @@
         <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F21">
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H21">
         <v>890</v>
@@ -1683,18 +1740,18 @@
         <v>10680</v>
       </c>
       <c r="J21" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="K21" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M21" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22">
-        <v>472</v>
+        <v>507</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
@@ -1706,33 +1763,33 @@
         <v>41</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F22">
         <v>320</v>
       </c>
       <c r="G22" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H22">
-        <v>185</v>
+        <v>102.53</v>
       </c>
       <c r="I22">
-        <v>59200</v>
+        <v>32809.6</v>
       </c>
       <c r="J22" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K22" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M22" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23">
-        <v>473</v>
+        <v>508</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
@@ -1744,33 +1801,33 @@
         <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F23">
         <v>192</v>
       </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H23">
-        <v>145</v>
+        <v>36.4</v>
       </c>
       <c r="I23">
-        <v>27840</v>
+        <v>6988.8</v>
       </c>
       <c r="J23" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K23" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M23" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24">
-        <v>474</v>
+        <v>509</v>
       </c>
       <c r="B24" t="s">
         <v>21</v>
@@ -1782,33 +1839,33 @@
         <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>224</v>
       </c>
       <c r="G24" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H24">
-        <v>210</v>
+        <v>81.78</v>
       </c>
       <c r="I24">
-        <v>47040</v>
+        <v>18318.72</v>
       </c>
       <c r="J24" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M24" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25">
-        <v>475</v>
+        <v>510</v>
       </c>
       <c r="B25" t="s">
         <v>21</v>
@@ -1820,33 +1877,33 @@
         <v>44</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F25">
         <v>224</v>
       </c>
       <c r="G25" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H25">
-        <v>210</v>
+        <v>186.85</v>
       </c>
       <c r="I25">
-        <v>47040</v>
+        <v>41854.4</v>
       </c>
       <c r="J25" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K25" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M25" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26">
-        <v>476</v>
+        <v>511</v>
       </c>
       <c r="B26" t="s">
         <v>21</v>
@@ -1858,33 +1915,33 @@
         <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F26">
         <v>160</v>
       </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H26">
-        <v>175</v>
+        <v>277.85</v>
       </c>
       <c r="I26">
-        <v>28000</v>
+        <v>44456</v>
       </c>
       <c r="J26" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K26" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M26" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27">
-        <v>477</v>
+        <v>512</v>
       </c>
       <c r="B27" t="s">
         <v>21</v>
@@ -1896,33 +1953,33 @@
         <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F27">
         <v>160</v>
       </c>
       <c r="G27" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H27">
-        <v>165</v>
+        <v>44.88</v>
       </c>
       <c r="I27">
-        <v>26400</v>
+        <v>7180.8</v>
       </c>
       <c r="J27" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K27" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M27" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28">
-        <v>478</v>
+        <v>513</v>
       </c>
       <c r="B28" t="s">
         <v>21</v>
@@ -1934,33 +1991,33 @@
         <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F28">
         <v>160</v>
       </c>
       <c r="G28" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H28">
-        <v>140</v>
+        <v>17.66</v>
       </c>
       <c r="I28">
-        <v>22400</v>
+        <v>2825.6</v>
       </c>
       <c r="J28" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K28" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M28" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29">
-        <v>479</v>
+        <v>514</v>
       </c>
       <c r="B29" t="s">
         <v>21</v>
@@ -1972,33 +2029,33 @@
         <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F29">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="G29" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H29">
-        <v>195</v>
+        <v>280.29</v>
       </c>
       <c r="I29">
-        <v>15600</v>
+        <v>35877.12</v>
       </c>
       <c r="J29" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K29" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M29" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30">
-        <v>480</v>
+        <v>515</v>
       </c>
       <c r="B30" t="s">
         <v>21</v>
@@ -2010,33 +2067,33 @@
         <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="F30">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G30" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H30">
-        <v>195</v>
+        <v>201.05</v>
       </c>
       <c r="I30">
-        <v>15600</v>
+        <v>32168</v>
       </c>
       <c r="J30" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K30" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M30" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31">
-        <v>481</v>
+        <v>516</v>
       </c>
       <c r="B31" t="s">
         <v>21</v>
@@ -2048,33 +2105,33 @@
         <v>50</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F31">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G31" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H31">
-        <v>230</v>
+        <v>137.55</v>
       </c>
       <c r="I31">
-        <v>27600</v>
+        <v>22008</v>
       </c>
       <c r="J31" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K31" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M31" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32">
-        <v>482</v>
+        <v>517</v>
       </c>
       <c r="B32" t="s">
         <v>21</v>
@@ -2086,33 +2143,33 @@
         <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F32">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H32">
-        <v>215</v>
+        <v>87.72</v>
       </c>
       <c r="I32">
-        <v>25800</v>
+        <v>8421.120000000001</v>
       </c>
       <c r="J32" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K32" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M32" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33">
-        <v>483</v>
+        <v>518</v>
       </c>
       <c r="B33" t="s">
         <v>21</v>
@@ -2124,33 +2181,33 @@
         <v>52</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F33">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H33">
-        <v>215</v>
+        <v>261.32</v>
       </c>
       <c r="I33">
-        <v>17200</v>
+        <v>25086.72</v>
       </c>
       <c r="J33" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K33" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M33" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34">
-        <v>484</v>
+        <v>519</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -2162,33 +2219,33 @@
         <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F34">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H34">
-        <v>155</v>
+        <v>308.26</v>
       </c>
       <c r="I34">
-        <v>12400</v>
+        <v>29592.96</v>
       </c>
       <c r="J34" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K34" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M34" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35">
-        <v>485</v>
+        <v>520</v>
       </c>
       <c r="B35" t="s">
         <v>21</v>
@@ -2200,33 +2257,33 @@
         <v>54</v>
       </c>
       <c r="E35" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F35">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H35">
-        <v>220</v>
+        <v>1270.07</v>
       </c>
       <c r="I35">
-        <v>35200</v>
+        <v>142247.84</v>
       </c>
       <c r="J35" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K35" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M35" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
@@ -2238,33 +2295,33 @@
         <v>55</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F36">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G36" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H36">
-        <v>210</v>
+        <v>541.41</v>
       </c>
       <c r="I36">
-        <v>25200</v>
+        <v>60637.92</v>
       </c>
       <c r="J36" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M36" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37">
-        <v>487</v>
+        <v>522</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
@@ -2276,33 +2333,33 @@
         <v>56</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="F37">
-        <v>240</v>
+        <v>112</v>
       </c>
       <c r="G37" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H37">
-        <v>245</v>
+        <v>541.41</v>
       </c>
       <c r="I37">
-        <v>58800</v>
+        <v>60637.92</v>
       </c>
       <c r="J37" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K37" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M37" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38">
-        <v>488</v>
+        <v>523</v>
       </c>
       <c r="B38" t="s">
         <v>21</v>
@@ -2314,33 +2371,33 @@
         <v>57</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F38">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H38">
-        <v>180</v>
+        <v>226.45</v>
       </c>
       <c r="I38">
-        <v>21600</v>
+        <v>18116</v>
       </c>
       <c r="J38" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K38" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M38" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39">
-        <v>489</v>
+        <v>524</v>
       </c>
       <c r="B39" t="s">
         <v>21</v>
@@ -2352,33 +2409,33 @@
         <v>58</v>
       </c>
       <c r="E39" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F39">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H39">
-        <v>180</v>
+        <v>226.45</v>
       </c>
       <c r="I39">
-        <v>21600</v>
+        <v>18116</v>
       </c>
       <c r="J39" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K39" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M39" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40">
-        <v>490</v>
+        <v>525</v>
       </c>
       <c r="B40" t="s">
         <v>21</v>
@@ -2390,33 +2447,33 @@
         <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F40">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H40">
-        <v>205</v>
+        <v>200.4</v>
       </c>
       <c r="I40">
-        <v>32800</v>
+        <v>16032</v>
       </c>
       <c r="J40" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K40" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M40" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41">
-        <v>491</v>
+        <v>526</v>
       </c>
       <c r="B41" t="s">
         <v>21</v>
@@ -2428,33 +2485,33 @@
         <v>60</v>
       </c>
       <c r="E41" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F41">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="G41" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H41">
-        <v>205</v>
+        <v>269</v>
       </c>
       <c r="I41">
-        <v>24600</v>
+        <v>17216</v>
       </c>
       <c r="J41" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K41" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M41" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42">
-        <v>492</v>
+        <v>527</v>
       </c>
       <c r="B42" t="s">
         <v>21</v>
@@ -2466,33 +2523,33 @@
         <v>61</v>
       </c>
       <c r="E42" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F42">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H42">
-        <v>205</v>
+        <v>202.76</v>
       </c>
       <c r="I42">
-        <v>32800</v>
+        <v>16220.8</v>
       </c>
       <c r="J42" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K42" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M42" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43">
-        <v>493</v>
+        <v>528</v>
       </c>
       <c r="B43" t="s">
         <v>21</v>
@@ -2504,33 +2561,33 @@
         <v>62</v>
       </c>
       <c r="E43" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F43">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="G43" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H43">
-        <v>205</v>
+        <v>109.33</v>
       </c>
       <c r="I43">
-        <v>24600</v>
+        <v>6997.12</v>
       </c>
       <c r="J43" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K43" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M43" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="B44" t="s">
         <v>21</v>
@@ -2542,33 +2599,33 @@
         <v>63</v>
       </c>
       <c r="E44" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F44">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G44" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H44">
-        <v>135</v>
+        <v>52.36</v>
       </c>
       <c r="I44">
-        <v>10800</v>
+        <v>3351.04</v>
       </c>
       <c r="J44" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K44" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M44" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45">
-        <v>495</v>
+        <v>530</v>
       </c>
       <c r="B45" t="s">
         <v>21</v>
@@ -2580,33 +2637,33 @@
         <v>64</v>
       </c>
       <c r="E45" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F45">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G45" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H45">
-        <v>135</v>
+        <v>123.01</v>
       </c>
       <c r="I45">
-        <v>10800</v>
+        <v>7872.64</v>
       </c>
       <c r="J45" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K45" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M45" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46">
-        <v>496</v>
+        <v>531</v>
       </c>
       <c r="B46" t="s">
         <v>21</v>
@@ -2618,33 +2675,33 @@
         <v>65</v>
       </c>
       <c r="E46" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F46">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G46" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H46">
-        <v>135</v>
+        <v>649.38</v>
       </c>
       <c r="I46">
-        <v>10800</v>
+        <v>41560.32</v>
       </c>
       <c r="J46" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K46" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M46" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="B47" t="s">
         <v>21</v>
@@ -2656,33 +2713,33 @@
         <v>66</v>
       </c>
       <c r="E47" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F47">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="G47" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H47">
-        <v>140</v>
+        <v>649.38</v>
       </c>
       <c r="I47">
-        <v>22400</v>
+        <v>41560.32</v>
       </c>
       <c r="J47" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K47" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M47" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48">
-        <v>498</v>
+        <v>533</v>
       </c>
       <c r="B48" t="s">
         <v>21</v>
@@ -2691,36 +2748,36 @@
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="E48" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F48">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G48" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H48">
-        <v>160</v>
+        <v>174.54</v>
       </c>
       <c r="I48">
-        <v>12800</v>
+        <v>11170.56</v>
       </c>
       <c r="J48" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K48" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M48" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49">
-        <v>499</v>
+        <v>534</v>
       </c>
       <c r="B49" t="s">
         <v>21</v>
@@ -2729,36 +2786,36 @@
         <v>28</v>
       </c>
       <c r="D49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E49" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F49">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G49" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H49">
-        <v>160</v>
+        <v>216.07</v>
       </c>
       <c r="I49">
-        <v>12800</v>
+        <v>8642.799999999999</v>
       </c>
       <c r="J49" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K49" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M49" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50">
-        <v>500</v>
+        <v>535</v>
       </c>
       <c r="B50" t="s">
         <v>21</v>
@@ -2767,36 +2824,36 @@
         <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E50" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G50" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H50">
-        <v>190</v>
+        <v>351.13</v>
       </c>
       <c r="I50">
-        <v>15200</v>
+        <v>14045.2</v>
       </c>
       <c r="J50" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K50" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M50" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51">
-        <v>501</v>
+        <v>536</v>
       </c>
       <c r="B51" t="s">
         <v>21</v>
@@ -2805,36 +2862,36 @@
         <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E51" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F51">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G51" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H51">
-        <v>190</v>
+        <v>361.57</v>
       </c>
       <c r="I51">
-        <v>15200</v>
+        <v>14462.8</v>
       </c>
       <c r="J51" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K51" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M51" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52">
-        <v>502</v>
+        <v>537</v>
       </c>
       <c r="B52" t="s">
         <v>21</v>
@@ -2843,36 +2900,36 @@
         <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E52" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F52">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="G52" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H52">
-        <v>115</v>
+        <v>83.48</v>
       </c>
       <c r="I52">
-        <v>18400</v>
+        <v>2671.36</v>
       </c>
       <c r="J52" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K52" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M52" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53">
-        <v>503</v>
+        <v>538</v>
       </c>
       <c r="B53" t="s">
         <v>21</v>
@@ -2881,36 +2938,36 @@
         <v>32</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E53" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F53">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="G53" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H53">
-        <v>115</v>
+        <v>251.07</v>
       </c>
       <c r="I53">
-        <v>18400</v>
+        <v>10042.8</v>
       </c>
       <c r="J53" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K53" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M53" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="B54" t="s">
         <v>21</v>
@@ -2919,36 +2976,36 @@
         <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E54" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F54">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G54" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H54">
-        <v>115</v>
+        <v>461.06</v>
       </c>
       <c r="I54">
-        <v>9200</v>
+        <v>18442.4</v>
       </c>
       <c r="J54" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K54" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M54" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55">
-        <v>505</v>
+        <v>540</v>
       </c>
       <c r="B55" t="s">
         <v>21</v>
@@ -2957,36 +3014,36 @@
         <v>34</v>
       </c>
       <c r="D55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E55" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F55">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="G55" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H55">
-        <v>115</v>
+        <v>461.06</v>
       </c>
       <c r="I55">
-        <v>18400</v>
+        <v>18442.4</v>
       </c>
       <c r="J55" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K55" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="M55" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56">
-        <v>506</v>
+        <v>541</v>
       </c>
       <c r="B56" t="s">
         <v>21</v>
@@ -2995,31 +3052,411 @@
         <v>35</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F56">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="G56" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H56">
+        <v>1123.34</v>
+      </c>
+      <c r="I56">
+        <v>44933.6</v>
+      </c>
+      <c r="J56" t="s">
+        <v>134</v>
+      </c>
+      <c r="K56" t="s">
+        <v>138</v>
+      </c>
+      <c r="M56" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="A57">
+        <v>542</v>
+      </c>
+      <c r="B57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57">
+        <v>36</v>
+      </c>
+      <c r="D57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57" t="s">
+        <v>124</v>
+      </c>
+      <c r="F57">
+        <v>32</v>
+      </c>
+      <c r="G57" t="s">
+        <v>132</v>
+      </c>
+      <c r="H57">
+        <v>187.32</v>
+      </c>
+      <c r="I57">
+        <v>5994.24</v>
+      </c>
+      <c r="J57" t="s">
+        <v>134</v>
+      </c>
+      <c r="K57" t="s">
+        <v>138</v>
+      </c>
+      <c r="M57" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="A58">
+        <v>543</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58">
+        <v>37</v>
+      </c>
+      <c r="D58" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58" t="s">
         <v>125</v>
       </c>
-      <c r="I56">
-        <v>15000</v>
-      </c>
-      <c r="J56" t="s">
+      <c r="F58">
+        <v>40</v>
+      </c>
+      <c r="G58" t="s">
+        <v>132</v>
+      </c>
+      <c r="H58">
+        <v>355.33</v>
+      </c>
+      <c r="I58">
+        <v>14213.2</v>
+      </c>
+      <c r="J58" t="s">
+        <v>134</v>
+      </c>
+      <c r="K58" t="s">
+        <v>138</v>
+      </c>
+      <c r="M58" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13">
+      <c r="A59">
+        <v>544</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59">
+        <v>38</v>
+      </c>
+      <c r="D59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" t="s">
+        <v>126</v>
+      </c>
+      <c r="F59">
+        <v>32</v>
+      </c>
+      <c r="G59" t="s">
+        <v>132</v>
+      </c>
+      <c r="H59">
+        <v>323.34</v>
+      </c>
+      <c r="I59">
+        <v>10346.88</v>
+      </c>
+      <c r="J59" t="s">
+        <v>134</v>
+      </c>
+      <c r="K59" t="s">
+        <v>138</v>
+      </c>
+      <c r="M59" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="A60">
+        <v>545</v>
+      </c>
+      <c r="B60" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60">
+        <v>39</v>
+      </c>
+      <c r="D60" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" t="s">
         <v>127</v>
       </c>
-      <c r="K56" t="s">
+      <c r="F60">
+        <v>32</v>
+      </c>
+      <c r="G60" t="s">
+        <v>132</v>
+      </c>
+      <c r="H60">
+        <v>614.42</v>
+      </c>
+      <c r="I60">
+        <v>19661.44</v>
+      </c>
+      <c r="J60" t="s">
+        <v>134</v>
+      </c>
+      <c r="K60" t="s">
+        <v>138</v>
+      </c>
+      <c r="M60" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61">
+        <v>546</v>
+      </c>
+      <c r="B61" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61">
+        <v>40</v>
+      </c>
+      <c r="D61" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" t="s">
+        <v>110</v>
+      </c>
+      <c r="F61">
+        <v>32</v>
+      </c>
+      <c r="G61" t="s">
+        <v>132</v>
+      </c>
+      <c r="H61">
+        <v>1371.31</v>
+      </c>
+      <c r="I61">
+        <v>43881.92</v>
+      </c>
+      <c r="J61" t="s">
+        <v>134</v>
+      </c>
+      <c r="K61" t="s">
+        <v>138</v>
+      </c>
+      <c r="M61" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
+      <c r="A62">
+        <v>547</v>
+      </c>
+      <c r="B62" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62">
+        <v>41</v>
+      </c>
+      <c r="D62" t="s">
+        <v>81</v>
+      </c>
+      <c r="E62" t="s">
+        <v>110</v>
+      </c>
+      <c r="F62">
+        <v>32</v>
+      </c>
+      <c r="G62" t="s">
+        <v>132</v>
+      </c>
+      <c r="H62">
+        <v>1648.76</v>
+      </c>
+      <c r="I62">
+        <v>52760.32</v>
+      </c>
+      <c r="J62" t="s">
+        <v>134</v>
+      </c>
+      <c r="K62" t="s">
+        <v>138</v>
+      </c>
+      <c r="M62" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63">
+        <v>548</v>
+      </c>
+      <c r="B63" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63">
+        <v>42</v>
+      </c>
+      <c r="D63" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63" t="s">
+        <v>128</v>
+      </c>
+      <c r="F63">
+        <v>32</v>
+      </c>
+      <c r="G63" t="s">
+        <v>132</v>
+      </c>
+      <c r="H63">
+        <v>614.42</v>
+      </c>
+      <c r="I63">
+        <v>19661.44</v>
+      </c>
+      <c r="J63" t="s">
+        <v>134</v>
+      </c>
+      <c r="K63" t="s">
+        <v>138</v>
+      </c>
+      <c r="M63" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64">
+        <v>549</v>
+      </c>
+      <c r="B64" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64">
+        <v>43</v>
+      </c>
+      <c r="D64" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64" t="s">
         <v>129</v>
       </c>
-      <c r="M56" t="s">
-        <v>180</v>
+      <c r="F64">
+        <v>40</v>
+      </c>
+      <c r="G64" t="s">
+        <v>132</v>
+      </c>
+      <c r="H64">
+        <v>769.6900000000001</v>
+      </c>
+      <c r="I64">
+        <v>30787.6</v>
+      </c>
+      <c r="J64" t="s">
+        <v>134</v>
+      </c>
+      <c r="K64" t="s">
+        <v>138</v>
+      </c>
+      <c r="M64" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13">
+      <c r="A65">
+        <v>550</v>
+      </c>
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65">
+        <v>44</v>
+      </c>
+      <c r="D65" t="s">
+        <v>83</v>
+      </c>
+      <c r="E65" t="s">
+        <v>130</v>
+      </c>
+      <c r="F65">
+        <v>32</v>
+      </c>
+      <c r="G65" t="s">
+        <v>132</v>
+      </c>
+      <c r="H65">
+        <v>856.38</v>
+      </c>
+      <c r="I65">
+        <v>27404.16</v>
+      </c>
+      <c r="J65" t="s">
+        <v>134</v>
+      </c>
+      <c r="K65" t="s">
+        <v>138</v>
+      </c>
+      <c r="M65" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
+      <c r="A66">
+        <v>551</v>
+      </c>
+      <c r="B66" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66">
+        <v>45</v>
+      </c>
+      <c r="D66" t="s">
+        <v>84</v>
+      </c>
+      <c r="E66" t="s">
+        <v>131</v>
+      </c>
+      <c r="F66">
+        <v>32</v>
+      </c>
+      <c r="G66" t="s">
+        <v>132</v>
+      </c>
+      <c r="H66">
+        <v>1644.8</v>
+      </c>
+      <c r="I66">
+        <v>52633.6</v>
+      </c>
+      <c r="J66" t="s">
+        <v>134</v>
+      </c>
+      <c r="K66" t="s">
+        <v>138</v>
+      </c>
+      <c r="M66" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_POs_Partidas_Detalladas.xlsx
+++ b/data/BD_POs_Partidas_Detalladas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="207">
   <si>
     <t>id_partida</t>
   </si>
@@ -82,6 +82,9 @@
     <t>26083425</t>
   </si>
   <si>
+    <t>26033022</t>
+  </si>
+  <si>
     <t>PP19380-03</t>
   </si>
   <si>
@@ -271,6 +274,9 @@
     <t>P19663-24</t>
   </si>
   <si>
+    <t>11-7761-03</t>
+  </si>
+  <si>
     <t>382 X 10H BLANK DOOR</t>
   </si>
   <si>
@@ -412,6 +418,12 @@
     <t>AUX PAN</t>
   </si>
   <si>
+    <t>11-7761-02 SOPORTE DE FIJACIÓN CLOUD</t>
+  </si>
+  <si>
+    <t>11-7761-03 SOPORTE DE FIJACIÓN META</t>
+  </si>
+  <si>
     <t>PIEZA</t>
   </si>
   <si>
@@ -430,7 +442,16 @@
     <t>2026-09-08</t>
   </si>
   <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
     <t>P1</t>
+  </si>
+  <si>
+    <t>Tarima TPM-0468 | Remisión E0116</t>
+  </si>
+  <si>
+    <t>Tarima TPM-0461 | Remisión E0109</t>
   </si>
   <si>
     <t>SWB01431</t>
@@ -945,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1000,16 +1021,16 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F2">
         <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H2">
         <v>345.5</v>
@@ -1018,13 +1039,13 @@
         <v>11056</v>
       </c>
       <c r="J2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1038,16 +1059,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F3">
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H3">
         <v>290</v>
@@ -1056,13 +1077,13 @@
         <v>2320</v>
       </c>
       <c r="J3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1076,16 +1097,16 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F4">
         <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H4">
         <v>290</v>
@@ -1094,13 +1115,13 @@
         <v>11600</v>
       </c>
       <c r="J4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1114,16 +1135,16 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H5">
         <v>850</v>
@@ -1132,13 +1153,13 @@
         <v>850</v>
       </c>
       <c r="J5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1152,16 +1173,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H6">
         <v>1089.57</v>
@@ -1170,13 +1191,13 @@
         <v>17433.12</v>
       </c>
       <c r="J6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M6" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1190,16 +1211,16 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>128</v>
       </c>
       <c r="G7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H7">
         <v>185.2</v>
@@ -1208,13 +1229,13 @@
         <v>23705.6</v>
       </c>
       <c r="J7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M7" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1228,16 +1249,16 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H8">
         <v>245.8</v>
@@ -1246,13 +1267,13 @@
         <v>7865.6</v>
       </c>
       <c r="J8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K8" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M8" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1266,16 +1287,16 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9">
         <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H9">
         <v>255.4</v>
@@ -1284,13 +1305,13 @@
         <v>10216</v>
       </c>
       <c r="J9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K9" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M9" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1304,16 +1325,16 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H10">
         <v>295</v>
@@ -1322,13 +1343,13 @@
         <v>18880</v>
       </c>
       <c r="J10" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K10" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1342,16 +1363,16 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11">
         <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H11">
         <v>295</v>
@@ -1360,13 +1381,13 @@
         <v>18880</v>
       </c>
       <c r="J11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K11" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1380,16 +1401,16 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12">
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H12">
         <v>245</v>
@@ -1398,13 +1419,13 @@
         <v>9800</v>
       </c>
       <c r="J12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M12" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1418,16 +1439,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F13">
         <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H13">
         <v>320.5</v>
@@ -1436,13 +1457,13 @@
         <v>10256</v>
       </c>
       <c r="J13" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K13" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M13" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -1456,16 +1477,16 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F14">
         <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H14">
         <v>345</v>
@@ -1474,13 +1495,13 @@
         <v>13800</v>
       </c>
       <c r="J14" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K14" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M14" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1494,16 +1515,16 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F15">
         <v>40</v>
       </c>
       <c r="G15" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H15">
         <v>270.2</v>
@@ -1512,13 +1533,13 @@
         <v>10807.85</v>
       </c>
       <c r="J15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K15" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M15" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1532,16 +1553,16 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F16">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H16">
         <v>420.5</v>
@@ -1550,13 +1571,13 @@
         <v>8410</v>
       </c>
       <c r="J16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K16" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1570,16 +1591,16 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F17">
         <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H17">
         <v>285</v>
@@ -1588,13 +1609,13 @@
         <v>9120</v>
       </c>
       <c r="J17" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1608,16 +1629,16 @@
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F18">
         <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H18">
         <v>195.75</v>
@@ -1626,13 +1647,13 @@
         <v>12528</v>
       </c>
       <c r="J18" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K18" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1646,16 +1667,16 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H19">
         <v>1250</v>
@@ -1664,13 +1685,13 @@
         <v>1250</v>
       </c>
       <c r="J19" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K19" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M19" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1684,16 +1705,16 @@
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H20">
         <v>680</v>
@@ -1702,13 +1723,13 @@
         <v>680</v>
       </c>
       <c r="J20" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K20" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1722,16 +1743,16 @@
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F21">
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H21">
         <v>890</v>
@@ -1740,13 +1761,13 @@
         <v>10680</v>
       </c>
       <c r="J21" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K21" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M21" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -1760,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>320</v>
       </c>
       <c r="G22" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H22">
         <v>102.53</v>
@@ -1778,13 +1799,13 @@
         <v>32809.6</v>
       </c>
       <c r="J22" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K22" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M22" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -1798,16 +1819,16 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F23">
         <v>192</v>
       </c>
       <c r="G23" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H23">
         <v>36.4</v>
@@ -1816,13 +1837,13 @@
         <v>6988.8</v>
       </c>
       <c r="J23" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K23" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M23" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -1836,16 +1857,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F24">
         <v>224</v>
       </c>
       <c r="G24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H24">
         <v>81.78</v>
@@ -1854,13 +1875,13 @@
         <v>18318.72</v>
       </c>
       <c r="J24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K24" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M24" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -1874,16 +1895,16 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F25">
         <v>224</v>
       </c>
       <c r="G25" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H25">
         <v>186.85</v>
@@ -1892,13 +1913,13 @@
         <v>41854.4</v>
       </c>
       <c r="J25" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K25" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M25" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1912,16 +1933,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F26">
         <v>160</v>
       </c>
       <c r="G26" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H26">
         <v>277.85</v>
@@ -1930,13 +1951,13 @@
         <v>44456</v>
       </c>
       <c r="J26" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K26" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M26" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1950,16 +1971,16 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F27">
         <v>160</v>
       </c>
       <c r="G27" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H27">
         <v>44.88</v>
@@ -1968,13 +1989,13 @@
         <v>7180.8</v>
       </c>
       <c r="J27" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K27" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M27" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1988,16 +2009,16 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F28">
         <v>160</v>
       </c>
       <c r="G28" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H28">
         <v>17.66</v>
@@ -2006,13 +2027,13 @@
         <v>2825.6</v>
       </c>
       <c r="J28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K28" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M28" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -2026,16 +2047,16 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F29">
         <v>128</v>
       </c>
       <c r="G29" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H29">
         <v>280.29</v>
@@ -2044,13 +2065,13 @@
         <v>35877.12</v>
       </c>
       <c r="J29" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K29" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M29" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -2064,16 +2085,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F30">
         <v>160</v>
       </c>
       <c r="G30" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H30">
         <v>201.05</v>
@@ -2082,13 +2103,13 @@
         <v>32168</v>
       </c>
       <c r="J30" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K30" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M30" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -2102,16 +2123,16 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F31">
         <v>160</v>
       </c>
       <c r="G31" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H31">
         <v>137.55</v>
@@ -2120,13 +2141,13 @@
         <v>22008</v>
       </c>
       <c r="J31" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K31" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M31" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -2140,16 +2161,16 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F32">
         <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H32">
         <v>87.72</v>
@@ -2158,13 +2179,13 @@
         <v>8421.120000000001</v>
       </c>
       <c r="J32" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K32" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M32" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -2178,16 +2199,16 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F33">
         <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H33">
         <v>261.32</v>
@@ -2196,13 +2217,13 @@
         <v>25086.72</v>
       </c>
       <c r="J33" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K33" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M33" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -2216,16 +2237,16 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E34" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F34">
         <v>96</v>
       </c>
       <c r="G34" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H34">
         <v>308.26</v>
@@ -2234,13 +2255,13 @@
         <v>29592.96</v>
       </c>
       <c r="J34" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K34" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M34" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -2254,16 +2275,16 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E35" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F35">
         <v>112</v>
       </c>
       <c r="G35" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H35">
         <v>1270.07</v>
@@ -2272,13 +2293,13 @@
         <v>142247.84</v>
       </c>
       <c r="J35" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K35" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M35" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -2292,16 +2313,16 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E36" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F36">
         <v>112</v>
       </c>
       <c r="G36" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H36">
         <v>541.41</v>
@@ -2310,13 +2331,13 @@
         <v>60637.92</v>
       </c>
       <c r="J36" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K36" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M36" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -2330,16 +2351,16 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E37" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F37">
         <v>112</v>
       </c>
       <c r="G37" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H37">
         <v>541.41</v>
@@ -2348,13 +2369,13 @@
         <v>60637.92</v>
       </c>
       <c r="J37" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K37" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M37" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -2368,16 +2389,16 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F38">
         <v>80</v>
       </c>
       <c r="G38" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H38">
         <v>226.45</v>
@@ -2386,13 +2407,13 @@
         <v>18116</v>
       </c>
       <c r="J38" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K38" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M38" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -2406,16 +2427,16 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F39">
         <v>80</v>
       </c>
       <c r="G39" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H39">
         <v>226.45</v>
@@ -2424,13 +2445,13 @@
         <v>18116</v>
       </c>
       <c r="J39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K39" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M39" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -2444,16 +2465,16 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F40">
         <v>80</v>
       </c>
       <c r="G40" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H40">
         <v>200.4</v>
@@ -2462,13 +2483,13 @@
         <v>16032</v>
       </c>
       <c r="J40" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K40" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M40" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -2482,16 +2503,16 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E41" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F41">
         <v>64</v>
       </c>
       <c r="G41" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H41">
         <v>269</v>
@@ -2500,13 +2521,13 @@
         <v>17216</v>
       </c>
       <c r="J41" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K41" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M41" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -2520,16 +2541,16 @@
         <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F42">
         <v>80</v>
       </c>
       <c r="G42" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H42">
         <v>202.76</v>
@@ -2538,13 +2559,13 @@
         <v>16220.8</v>
       </c>
       <c r="J42" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K42" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M42" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -2558,16 +2579,16 @@
         <v>22</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F43">
         <v>64</v>
       </c>
       <c r="G43" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H43">
         <v>109.33</v>
@@ -2576,13 +2597,13 @@
         <v>6997.12</v>
       </c>
       <c r="J43" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K43" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M43" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -2596,16 +2617,16 @@
         <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F44">
         <v>64</v>
       </c>
       <c r="G44" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H44">
         <v>52.36</v>
@@ -2614,13 +2635,13 @@
         <v>3351.04</v>
       </c>
       <c r="J44" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K44" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M44" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -2634,16 +2655,16 @@
         <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F45">
         <v>64</v>
       </c>
       <c r="G45" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H45">
         <v>123.01</v>
@@ -2652,13 +2673,13 @@
         <v>7872.64</v>
       </c>
       <c r="J45" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K45" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M45" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2672,16 +2693,16 @@
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E46" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F46">
         <v>64</v>
       </c>
       <c r="G46" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H46">
         <v>649.38</v>
@@ -2690,13 +2711,13 @@
         <v>41560.32</v>
       </c>
       <c r="J46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K46" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M46" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -2710,16 +2731,16 @@
         <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F47">
         <v>64</v>
       </c>
       <c r="G47" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H47">
         <v>649.38</v>
@@ -2728,13 +2749,13 @@
         <v>41560.32</v>
       </c>
       <c r="J47" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K47" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M47" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -2748,16 +2769,16 @@
         <v>27</v>
       </c>
       <c r="D48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F48">
         <v>64</v>
       </c>
       <c r="G48" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H48">
         <v>174.54</v>
@@ -2766,13 +2787,13 @@
         <v>11170.56</v>
       </c>
       <c r="J48" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K48" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M48" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -2786,16 +2807,16 @@
         <v>28</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F49">
         <v>40</v>
       </c>
       <c r="G49" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H49">
         <v>216.07</v>
@@ -2804,13 +2825,13 @@
         <v>8642.799999999999</v>
       </c>
       <c r="J49" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K49" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M49" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -2824,16 +2845,16 @@
         <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E50" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F50">
         <v>40</v>
       </c>
       <c r="G50" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H50">
         <v>351.13</v>
@@ -2842,13 +2863,13 @@
         <v>14045.2</v>
       </c>
       <c r="J50" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K50" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M50" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -2862,16 +2883,16 @@
         <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E51" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F51">
         <v>40</v>
       </c>
       <c r="G51" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H51">
         <v>361.57</v>
@@ -2880,13 +2901,13 @@
         <v>14462.8</v>
       </c>
       <c r="J51" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K51" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M51" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -2900,16 +2921,16 @@
         <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E52" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F52">
         <v>32</v>
       </c>
       <c r="G52" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H52">
         <v>83.48</v>
@@ -2918,13 +2939,13 @@
         <v>2671.36</v>
       </c>
       <c r="J52" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K52" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M52" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -2938,16 +2959,16 @@
         <v>32</v>
       </c>
       <c r="D53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E53" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F53">
         <v>40</v>
       </c>
       <c r="G53" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H53">
         <v>251.07</v>
@@ -2956,13 +2977,13 @@
         <v>10042.8</v>
       </c>
       <c r="J53" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K53" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M53" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -2976,16 +2997,16 @@
         <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E54" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F54">
         <v>40</v>
       </c>
       <c r="G54" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H54">
         <v>461.06</v>
@@ -2994,13 +3015,13 @@
         <v>18442.4</v>
       </c>
       <c r="J54" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K54" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M54" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -3014,16 +3035,16 @@
         <v>34</v>
       </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E55" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F55">
         <v>40</v>
       </c>
       <c r="G55" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H55">
         <v>461.06</v>
@@ -3032,13 +3053,13 @@
         <v>18442.4</v>
       </c>
       <c r="J55" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K55" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M55" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -3052,16 +3073,16 @@
         <v>35</v>
       </c>
       <c r="D56" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E56" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F56">
         <v>40</v>
       </c>
       <c r="G56" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H56">
         <v>1123.34</v>
@@ -3070,13 +3091,13 @@
         <v>44933.6</v>
       </c>
       <c r="J56" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K56" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M56" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -3090,16 +3111,16 @@
         <v>36</v>
       </c>
       <c r="D57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F57">
         <v>32</v>
       </c>
       <c r="G57" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H57">
         <v>187.32</v>
@@ -3108,13 +3129,13 @@
         <v>5994.24</v>
       </c>
       <c r="J57" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K57" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M57" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -3128,16 +3149,16 @@
         <v>37</v>
       </c>
       <c r="D58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E58" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F58">
         <v>40</v>
       </c>
       <c r="G58" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H58">
         <v>355.33</v>
@@ -3146,13 +3167,13 @@
         <v>14213.2</v>
       </c>
       <c r="J58" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K58" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M58" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -3166,16 +3187,16 @@
         <v>38</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E59" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F59">
         <v>32</v>
       </c>
       <c r="G59" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H59">
         <v>323.34</v>
@@ -3184,13 +3205,13 @@
         <v>10346.88</v>
       </c>
       <c r="J59" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K59" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M59" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -3204,16 +3225,16 @@
         <v>39</v>
       </c>
       <c r="D60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E60" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F60">
         <v>32</v>
       </c>
       <c r="G60" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H60">
         <v>614.42</v>
@@ -3222,13 +3243,13 @@
         <v>19661.44</v>
       </c>
       <c r="J60" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K60" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M60" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -3242,16 +3263,16 @@
         <v>40</v>
       </c>
       <c r="D61" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E61" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F61">
         <v>32</v>
       </c>
       <c r="G61" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H61">
         <v>1371.31</v>
@@ -3260,13 +3281,13 @@
         <v>43881.92</v>
       </c>
       <c r="J61" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K61" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M61" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -3280,16 +3301,16 @@
         <v>41</v>
       </c>
       <c r="D62" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E62" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F62">
         <v>32</v>
       </c>
       <c r="G62" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H62">
         <v>1648.76</v>
@@ -3298,13 +3319,13 @@
         <v>52760.32</v>
       </c>
       <c r="J62" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K62" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M62" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -3318,16 +3339,16 @@
         <v>42</v>
       </c>
       <c r="D63" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E63" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F63">
         <v>32</v>
       </c>
       <c r="G63" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H63">
         <v>614.42</v>
@@ -3336,13 +3357,13 @@
         <v>19661.44</v>
       </c>
       <c r="J63" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K63" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M63" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -3356,16 +3377,16 @@
         <v>43</v>
       </c>
       <c r="D64" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F64">
         <v>40</v>
       </c>
       <c r="G64" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H64">
         <v>769.6900000000001</v>
@@ -3374,13 +3395,13 @@
         <v>30787.6</v>
       </c>
       <c r="J64" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K64" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M64" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -3394,16 +3415,16 @@
         <v>44</v>
       </c>
       <c r="D65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E65" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F65">
         <v>32</v>
       </c>
       <c r="G65" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H65">
         <v>856.38</v>
@@ -3412,13 +3433,13 @@
         <v>27404.16</v>
       </c>
       <c r="J65" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K65" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M65" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -3432,16 +3453,16 @@
         <v>45</v>
       </c>
       <c r="D66" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E66" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F66">
         <v>32</v>
       </c>
       <c r="G66" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H66">
         <v>1644.8</v>
@@ -3450,13 +3471,95 @@
         <v>52633.6</v>
       </c>
       <c r="J66" t="s">
+        <v>138</v>
+      </c>
+      <c r="K66" t="s">
+        <v>143</v>
+      </c>
+      <c r="M66" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
+      <c r="A67">
+        <v>552</v>
+      </c>
+      <c r="B67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" t="s">
         <v>134</v>
       </c>
-      <c r="K66" t="s">
-        <v>138</v>
-      </c>
-      <c r="M66" t="s">
-        <v>199</v>
+      <c r="F67">
+        <v>73</v>
+      </c>
+      <c r="G67" t="s">
+        <v>136</v>
+      </c>
+      <c r="H67">
+        <v>290</v>
+      </c>
+      <c r="I67">
+        <v>21170</v>
+      </c>
+      <c r="J67" t="s">
+        <v>142</v>
+      </c>
+      <c r="K67" t="s">
+        <v>143</v>
+      </c>
+      <c r="L67" t="s">
+        <v>144</v>
+      </c>
+      <c r="M67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
+      <c r="A68">
+        <v>553</v>
+      </c>
+      <c r="B68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68" t="s">
+        <v>86</v>
+      </c>
+      <c r="E68" t="s">
+        <v>135</v>
+      </c>
+      <c r="F68">
+        <v>4</v>
+      </c>
+      <c r="G68" t="s">
+        <v>136</v>
+      </c>
+      <c r="H68">
+        <v>290</v>
+      </c>
+      <c r="I68">
+        <v>1160</v>
+      </c>
+      <c r="J68" t="s">
+        <v>142</v>
+      </c>
+      <c r="K68" t="s">
+        <v>143</v>
+      </c>
+      <c r="L68" t="s">
+        <v>145</v>
+      </c>
+      <c r="M68" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/data/BD_POs_Partidas_Detalladas.xlsx
+++ b/data/BD_POs_Partidas_Detalladas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7412" uniqueCount="1390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7412" uniqueCount="1389">
   <si>
     <t>id_partida</t>
   </si>
@@ -1504,7 +1504,7 @@
     <t>11-E-9851-01</t>
   </si>
   <si>
-    <t>11-E-9851-02 - COMPARTIMIENTO AUXILIAR</t>
+    <t>11-E-9851-02</t>
   </si>
   <si>
     <t>11-E-9870-02</t>
@@ -4151,9 +4151,6 @@
   </si>
   <si>
     <t>SWB01941</t>
-  </si>
-  <si>
-    <t>11-E-9851-02</t>
   </si>
   <si>
     <t>ISSIV05319</t>
@@ -44342,7 +44339,7 @@
         <v>959</v>
       </c>
       <c r="M1048" t="s">
-        <v>1379</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1049" spans="1:13">
@@ -44380,7 +44377,7 @@
         <v>959</v>
       </c>
       <c r="M1049" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="1050" spans="1:13">
@@ -44418,7 +44415,7 @@
         <v>959</v>
       </c>
       <c r="M1050" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="1051" spans="1:13">
@@ -44456,7 +44453,7 @@
         <v>959</v>
       </c>
       <c r="M1051" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="1052" spans="1:13">
@@ -44494,7 +44491,7 @@
         <v>959</v>
       </c>
       <c r="M1052" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="1053" spans="1:13">
@@ -44532,7 +44529,7 @@
         <v>959</v>
       </c>
       <c r="M1053" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="1054" spans="1:13">
@@ -44570,7 +44567,7 @@
         <v>959</v>
       </c>
       <c r="M1054" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="1055" spans="1:13">
@@ -44608,7 +44605,7 @@
         <v>959</v>
       </c>
       <c r="M1055" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="1056" spans="1:13">
@@ -44646,7 +44643,7 @@
         <v>959</v>
       </c>
       <c r="M1056" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="1057" spans="1:13">
@@ -44684,7 +44681,7 @@
         <v>959</v>
       </c>
       <c r="M1057" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="1058" spans="1:13">
@@ -44722,7 +44719,7 @@
         <v>959</v>
       </c>
       <c r="M1058" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
   </sheetData>
